--- a/Bin Oct Hex.xlsx
+++ b/Bin Oct Hex.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28925"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29426"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="H:\_cwg-base__Home\Computer Archtecture\Retro Computing\SBC6502\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{57F7F9E7-DAC7-4766-A796-50554967104A}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{774BC730-5332-4381-9118-4DC715FF08A5}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="780" yWindow="780" windowWidth="28800" windowHeight="11235" xr2:uid="{E2CDCCBC-594B-4A42-BA3F-95D5E3C9B4E3}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{E2CDCCBC-594B-4A42-BA3F-95D5E3C9B4E3}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -465,17 +465,17 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{28045FA7-E967-4EB5-BE87-47BB5AA2AF07}">
   <dimension ref="A1:H1048"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="21.28515625" style="1" customWidth="1"/>
-    <col min="2" max="2" width="9.7109375" style="2" customWidth="1"/>
-    <col min="3" max="4" width="10.7109375" style="2" customWidth="1"/>
-    <col min="5" max="5" width="10.7109375" style="1" customWidth="1"/>
-    <col min="6" max="6" width="25.140625" style="2" bestFit="1" customWidth="1"/>
-    <col min="7" max="8" width="9.28515625" style="1"/>
+    <col min="1" max="1" width="21.33203125" style="1" customWidth="1"/>
+    <col min="2" max="2" width="9.6640625" style="2" customWidth="1"/>
+    <col min="3" max="4" width="10.6640625" style="2" customWidth="1"/>
+    <col min="5" max="5" width="10.6640625" style="1" customWidth="1"/>
+    <col min="6" max="6" width="26.6640625" style="2" bestFit="1" customWidth="1"/>
+    <col min="7" max="8" width="9.33203125" style="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:4" x14ac:dyDescent="0.3">
       <c r="B1" s="5" t="s">
         <v>6</v>
       </c>
@@ -483,7 +483,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="2" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A2" s="4" t="s">
         <v>13</v>
       </c>
@@ -495,7 +495,7 @@
         <v>65536</v>
       </c>
     </row>
-    <row r="3" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A3" s="4" t="s">
         <v>12</v>
       </c>
@@ -507,7 +507,7 @@
         <v>1048576</v>
       </c>
     </row>
-    <row r="4" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A4" s="4" t="s">
         <v>8</v>
       </c>
@@ -519,7 +519,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="5" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="5" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A5" s="4" t="s">
         <v>11</v>
       </c>
@@ -532,7 +532,7 @@
         <v>1024</v>
       </c>
     </row>
-    <row r="6" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A6" s="4" t="s">
         <v>9</v>
       </c>
@@ -544,7 +544,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="7" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A7" s="4" t="s">
         <v>10</v>
       </c>
@@ -561,7 +561,7 @@
         <v>64/PID</v>
       </c>
     </row>
-    <row r="9" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A9" s="4" t="s">
         <v>13</v>
       </c>
@@ -573,7 +573,7 @@
         <v>65536</v>
       </c>
     </row>
-    <row r="10" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A10" s="4" t="s">
         <v>12</v>
       </c>
@@ -585,7 +585,7 @@
         <v>1048576</v>
       </c>
     </row>
-    <row r="11" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A11" s="4" t="s">
         <v>8</v>
       </c>
@@ -597,7 +597,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="12" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="12" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A12" s="4" t="s">
         <v>11</v>
       </c>
@@ -610,7 +610,7 @@
         <v>4096</v>
       </c>
     </row>
-    <row r="13" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="13" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A13" s="4" t="s">
         <v>9</v>
       </c>
@@ -622,7 +622,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="14" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="14" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A14" s="4" t="s">
         <v>10</v>
       </c>
@@ -639,7 +639,7 @@
         <v>256/PID</v>
       </c>
     </row>
-    <row r="16" spans="1:4" x14ac:dyDescent="0.25">
+    <row r="16" spans="1:4" x14ac:dyDescent="0.3">
       <c r="A16" s="4" t="s">
         <v>13</v>
       </c>
@@ -651,7 +651,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="17" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="17" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A17" s="4" t="s">
         <v>12</v>
       </c>
@@ -663,7 +663,7 @@
         <v>256</v>
       </c>
     </row>
-    <row r="18" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="18" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A18" s="4" t="s">
         <v>8</v>
       </c>
@@ -675,7 +675,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="19" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="19" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A19" s="4" t="s">
         <v>11</v>
       </c>
@@ -688,7 +688,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="20" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="20" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A20" s="4" t="s">
         <v>9</v>
       </c>
@@ -700,7 +700,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="21" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="21" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A21" s="4" t="s">
         <v>10</v>
       </c>
@@ -717,10 +717,10 @@
         <v>4/PID</v>
       </c>
     </row>
-    <row r="22" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="22" spans="1:8" x14ac:dyDescent="0.3">
       <c r="A22" s="4"/>
     </row>
-    <row r="23" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.25">
+    <row r="23" spans="1:8" s="4" customFormat="1" x14ac:dyDescent="0.3">
       <c r="B23" s="5"/>
       <c r="C23" s="5" t="s">
         <v>3</v>
@@ -741,7 +741,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="24" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="24" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B24" s="2">
         <v>0</v>
       </c>
@@ -762,7 +762,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="25" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="25" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B25" s="2">
         <v>1</v>
       </c>
@@ -791,7 +791,7 @@
         <v>00000F</v>
       </c>
     </row>
-    <row r="26" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="26" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B26" s="2">
         <v>2</v>
       </c>
@@ -820,7 +820,7 @@
         <v>00001F</v>
       </c>
     </row>
-    <row r="27" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="27" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B27" s="2">
         <v>3</v>
       </c>
@@ -849,7 +849,7 @@
         <v>00002F</v>
       </c>
     </row>
-    <row r="28" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="28" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B28" s="2">
         <v>4</v>
       </c>
@@ -878,7 +878,7 @@
         <v>00003F</v>
       </c>
     </row>
-    <row r="29" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="29" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B29" s="2">
         <v>5</v>
       </c>
@@ -907,7 +907,7 @@
         <v>00004F</v>
       </c>
     </row>
-    <row r="30" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="30" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B30" s="2">
         <v>6</v>
       </c>
@@ -936,7 +936,7 @@
         <v>00005F</v>
       </c>
     </row>
-    <row r="31" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="31" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B31" s="2">
         <v>7</v>
       </c>
@@ -965,7 +965,7 @@
         <v>00006F</v>
       </c>
     </row>
-    <row r="32" spans="1:8" x14ac:dyDescent="0.25">
+    <row r="32" spans="1:8" x14ac:dyDescent="0.3">
       <c r="B32" s="2">
         <v>8</v>
       </c>
@@ -994,7 +994,7 @@
         <v>00007F</v>
       </c>
     </row>
-    <row r="33" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="33" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B33" s="2">
         <v>9</v>
       </c>
@@ -1023,7 +1023,7 @@
         <v>00008F</v>
       </c>
     </row>
-    <row r="34" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="34" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B34" s="2">
         <v>10</v>
       </c>
@@ -1052,7 +1052,7 @@
         <v>00009F</v>
       </c>
     </row>
-    <row r="35" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="35" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B35" s="2">
         <v>11</v>
       </c>
@@ -1081,7 +1081,7 @@
         <v>0000AF</v>
       </c>
     </row>
-    <row r="36" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="36" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B36" s="2">
         <v>12</v>
       </c>
@@ -1110,7 +1110,7 @@
         <v>0000BF</v>
       </c>
     </row>
-    <row r="37" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="37" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B37" s="2">
         <v>13</v>
       </c>
@@ -1139,7 +1139,7 @@
         <v>0000CF</v>
       </c>
     </row>
-    <row r="38" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="38" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B38" s="2">
         <v>14</v>
       </c>
@@ -1168,7 +1168,7 @@
         <v>0000DF</v>
       </c>
     </row>
-    <row r="39" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="39" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B39" s="2">
         <v>15</v>
       </c>
@@ -1197,7 +1197,7 @@
         <v>0000EF</v>
       </c>
     </row>
-    <row r="40" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="40" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B40" s="2">
         <v>16</v>
       </c>
@@ -1226,7 +1226,7 @@
         <v>0000FF</v>
       </c>
     </row>
-    <row r="41" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="41" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B41" s="2">
         <v>17</v>
       </c>
@@ -1255,7 +1255,7 @@
         <v>00010F</v>
       </c>
     </row>
-    <row r="42" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="42" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B42" s="2">
         <v>18</v>
       </c>
@@ -1284,7 +1284,7 @@
         <v>00011F</v>
       </c>
     </row>
-    <row r="43" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="43" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B43" s="2">
         <v>19</v>
       </c>
@@ -1313,7 +1313,7 @@
         <v>00012F</v>
       </c>
     </row>
-    <row r="44" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="44" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B44" s="2">
         <v>20</v>
       </c>
@@ -1342,7 +1342,7 @@
         <v>00013F</v>
       </c>
     </row>
-    <row r="45" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="45" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B45" s="2">
         <v>21</v>
       </c>
@@ -1371,7 +1371,7 @@
         <v>00014F</v>
       </c>
     </row>
-    <row r="46" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="46" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B46" s="2">
         <v>22</v>
       </c>
@@ -1400,7 +1400,7 @@
         <v>00015F</v>
       </c>
     </row>
-    <row r="47" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="47" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B47" s="2">
         <v>23</v>
       </c>
@@ -1429,7 +1429,7 @@
         <v>00016F</v>
       </c>
     </row>
-    <row r="48" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="48" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B48" s="2">
         <v>24</v>
       </c>
@@ -1458,7 +1458,7 @@
         <v>00017F</v>
       </c>
     </row>
-    <row r="49" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="49" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B49" s="2">
         <v>25</v>
       </c>
@@ -1487,7 +1487,7 @@
         <v>00018F</v>
       </c>
     </row>
-    <row r="50" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="50" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B50" s="2">
         <v>26</v>
       </c>
@@ -1516,7 +1516,7 @@
         <v>00019F</v>
       </c>
     </row>
-    <row r="51" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="51" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B51" s="2">
         <v>27</v>
       </c>
@@ -1545,7 +1545,7 @@
         <v>0001AF</v>
       </c>
     </row>
-    <row r="52" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="52" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B52" s="2">
         <v>28</v>
       </c>
@@ -1574,7 +1574,7 @@
         <v>0001BF</v>
       </c>
     </row>
-    <row r="53" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="53" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B53" s="2">
         <v>29</v>
       </c>
@@ -1603,7 +1603,7 @@
         <v>0001CF</v>
       </c>
     </row>
-    <row r="54" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="54" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B54" s="2">
         <v>30</v>
       </c>
@@ -1632,7 +1632,7 @@
         <v>0001DF</v>
       </c>
     </row>
-    <row r="55" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="55" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B55" s="2">
         <v>31</v>
       </c>
@@ -1661,7 +1661,7 @@
         <v>0001EF</v>
       </c>
     </row>
-    <row r="56" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="56" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B56" s="2">
         <v>32</v>
       </c>
@@ -1690,7 +1690,7 @@
         <v>0001FF</v>
       </c>
     </row>
-    <row r="57" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="57" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B57" s="2">
         <v>33</v>
       </c>
@@ -1719,7 +1719,7 @@
         <v>00020F</v>
       </c>
     </row>
-    <row r="58" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="58" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B58" s="2">
         <v>34</v>
       </c>
@@ -1748,7 +1748,7 @@
         <v>00021F</v>
       </c>
     </row>
-    <row r="59" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="59" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B59" s="2">
         <v>35</v>
       </c>
@@ -1777,7 +1777,7 @@
         <v>00022F</v>
       </c>
     </row>
-    <row r="60" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="60" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B60" s="2">
         <v>36</v>
       </c>
@@ -1806,7 +1806,7 @@
         <v>00023F</v>
       </c>
     </row>
-    <row r="61" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="61" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B61" s="2">
         <v>37</v>
       </c>
@@ -1835,7 +1835,7 @@
         <v>00024F</v>
       </c>
     </row>
-    <row r="62" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="62" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B62" s="2">
         <v>38</v>
       </c>
@@ -1864,7 +1864,7 @@
         <v>00025F</v>
       </c>
     </row>
-    <row r="63" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="63" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B63" s="2">
         <v>39</v>
       </c>
@@ -1893,7 +1893,7 @@
         <v>00026F</v>
       </c>
     </row>
-    <row r="64" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="64" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B64" s="2">
         <v>40</v>
       </c>
@@ -1922,7 +1922,7 @@
         <v>00027F</v>
       </c>
     </row>
-    <row r="65" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="65" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B65" s="2">
         <v>41</v>
       </c>
@@ -1951,7 +1951,7 @@
         <v>00028F</v>
       </c>
     </row>
-    <row r="66" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="66" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B66" s="2">
         <v>42</v>
       </c>
@@ -1980,7 +1980,7 @@
         <v>00029F</v>
       </c>
     </row>
-    <row r="67" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="67" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B67" s="2">
         <v>43</v>
       </c>
@@ -2009,7 +2009,7 @@
         <v>0002AF</v>
       </c>
     </row>
-    <row r="68" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="68" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B68" s="2">
         <v>44</v>
       </c>
@@ -2038,7 +2038,7 @@
         <v>0002BF</v>
       </c>
     </row>
-    <row r="69" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="69" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B69" s="2">
         <v>45</v>
       </c>
@@ -2067,7 +2067,7 @@
         <v>0002CF</v>
       </c>
     </row>
-    <row r="70" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="70" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B70" s="2">
         <v>46</v>
       </c>
@@ -2096,7 +2096,7 @@
         <v>0002DF</v>
       </c>
     </row>
-    <row r="71" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="71" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B71" s="2">
         <v>47</v>
       </c>
@@ -2125,7 +2125,7 @@
         <v>0002EF</v>
       </c>
     </row>
-    <row r="72" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="72" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B72" s="2">
         <v>48</v>
       </c>
@@ -2154,7 +2154,7 @@
         <v>0002FF</v>
       </c>
     </row>
-    <row r="73" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="73" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B73" s="2">
         <v>49</v>
       </c>
@@ -2183,7 +2183,7 @@
         <v>00030F</v>
       </c>
     </row>
-    <row r="74" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="74" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B74" s="2">
         <v>50</v>
       </c>
@@ -2212,7 +2212,7 @@
         <v>00031F</v>
       </c>
     </row>
-    <row r="75" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="75" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B75" s="2">
         <v>51</v>
       </c>
@@ -2241,7 +2241,7 @@
         <v>00032F</v>
       </c>
     </row>
-    <row r="76" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="76" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B76" s="2">
         <v>52</v>
       </c>
@@ -2270,7 +2270,7 @@
         <v>00033F</v>
       </c>
     </row>
-    <row r="77" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="77" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B77" s="2">
         <v>53</v>
       </c>
@@ -2299,7 +2299,7 @@
         <v>00034F</v>
       </c>
     </row>
-    <row r="78" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="78" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B78" s="2">
         <v>54</v>
       </c>
@@ -2328,7 +2328,7 @@
         <v>00035F</v>
       </c>
     </row>
-    <row r="79" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="79" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B79" s="2">
         <v>55</v>
       </c>
@@ -2357,7 +2357,7 @@
         <v>00036F</v>
       </c>
     </row>
-    <row r="80" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="80" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B80" s="2">
         <v>56</v>
       </c>
@@ -2386,7 +2386,7 @@
         <v>00037F</v>
       </c>
     </row>
-    <row r="81" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="81" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B81" s="2">
         <v>57</v>
       </c>
@@ -2415,7 +2415,7 @@
         <v>00038F</v>
       </c>
     </row>
-    <row r="82" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="82" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B82" s="2">
         <v>58</v>
       </c>
@@ -2444,7 +2444,7 @@
         <v>00039F</v>
       </c>
     </row>
-    <row r="83" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="83" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B83" s="2">
         <v>59</v>
       </c>
@@ -2473,7 +2473,7 @@
         <v>0003AF</v>
       </c>
     </row>
-    <row r="84" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="84" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B84" s="2">
         <v>60</v>
       </c>
@@ -2502,7 +2502,7 @@
         <v>0003BF</v>
       </c>
     </row>
-    <row r="85" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="85" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B85" s="2">
         <v>61</v>
       </c>
@@ -2531,7 +2531,7 @@
         <v>0003CF</v>
       </c>
     </row>
-    <row r="86" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="86" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B86" s="2">
         <v>62</v>
       </c>
@@ -2560,7 +2560,7 @@
         <v>0003DF</v>
       </c>
     </row>
-    <row r="87" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="87" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B87" s="2">
         <v>63</v>
       </c>
@@ -2589,7 +2589,7 @@
         <v>0003EF</v>
       </c>
     </row>
-    <row r="88" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="88" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B88" s="2">
         <v>64</v>
       </c>
@@ -2618,7 +2618,7 @@
         <v>0003FF</v>
       </c>
     </row>
-    <row r="89" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="89" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B89" s="2">
         <v>65</v>
       </c>
@@ -2643,7 +2643,7 @@
         <v>00040F</v>
       </c>
     </row>
-    <row r="90" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="90" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B90" s="2">
         <v>66</v>
       </c>
@@ -2668,7 +2668,7 @@
         <v>00041F</v>
       </c>
     </row>
-    <row r="91" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="91" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B91" s="2">
         <v>67</v>
       </c>
@@ -2693,7 +2693,7 @@
         <v>00042F</v>
       </c>
     </row>
-    <row r="92" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="92" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B92" s="2">
         <v>68</v>
       </c>
@@ -2718,7 +2718,7 @@
         <v>00043F</v>
       </c>
     </row>
-    <row r="93" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="93" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B93" s="2">
         <v>69</v>
       </c>
@@ -2743,7 +2743,7 @@
         <v>00044F</v>
       </c>
     </row>
-    <row r="94" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="94" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B94" s="2">
         <v>70</v>
       </c>
@@ -2768,7 +2768,7 @@
         <v>00045F</v>
       </c>
     </row>
-    <row r="95" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="95" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B95" s="2">
         <v>71</v>
       </c>
@@ -2793,7 +2793,7 @@
         <v>00046F</v>
       </c>
     </row>
-    <row r="96" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="96" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B96" s="2">
         <v>72</v>
       </c>
@@ -2818,7 +2818,7 @@
         <v>00047F</v>
       </c>
     </row>
-    <row r="97" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="97" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B97" s="2">
         <v>73</v>
       </c>
@@ -2843,7 +2843,7 @@
         <v>00048F</v>
       </c>
     </row>
-    <row r="98" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="98" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B98" s="2">
         <v>74</v>
       </c>
@@ -2868,7 +2868,7 @@
         <v>00049F</v>
       </c>
     </row>
-    <row r="99" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="99" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B99" s="2">
         <v>75</v>
       </c>
@@ -2893,7 +2893,7 @@
         <v>0004AF</v>
       </c>
     </row>
-    <row r="100" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="100" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B100" s="2">
         <v>76</v>
       </c>
@@ -2918,7 +2918,7 @@
         <v>0004BF</v>
       </c>
     </row>
-    <row r="101" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="101" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B101" s="2">
         <v>77</v>
       </c>
@@ -2943,7 +2943,7 @@
         <v>0004CF</v>
       </c>
     </row>
-    <row r="102" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="102" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B102" s="2">
         <v>78</v>
       </c>
@@ -2968,7 +2968,7 @@
         <v>0004DF</v>
       </c>
     </row>
-    <row r="103" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="103" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B103" s="2">
         <v>79</v>
       </c>
@@ -2993,7 +2993,7 @@
         <v>0004EF</v>
       </c>
     </row>
-    <row r="104" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="104" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B104" s="2">
         <v>80</v>
       </c>
@@ -3018,7 +3018,7 @@
         <v>0004FF</v>
       </c>
     </row>
-    <row r="105" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="105" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B105" s="2">
         <v>81</v>
       </c>
@@ -3043,7 +3043,7 @@
         <v>00050F</v>
       </c>
     </row>
-    <row r="106" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="106" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B106" s="2">
         <v>82</v>
       </c>
@@ -3068,7 +3068,7 @@
         <v>00051F</v>
       </c>
     </row>
-    <row r="107" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="107" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B107" s="2">
         <v>83</v>
       </c>
@@ -3093,7 +3093,7 @@
         <v>00052F</v>
       </c>
     </row>
-    <row r="108" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="108" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B108" s="2">
         <v>84</v>
       </c>
@@ -3118,7 +3118,7 @@
         <v>00053F</v>
       </c>
     </row>
-    <row r="109" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="109" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B109" s="2">
         <v>85</v>
       </c>
@@ -3143,7 +3143,7 @@
         <v>00054F</v>
       </c>
     </row>
-    <row r="110" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="110" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B110" s="2">
         <v>86</v>
       </c>
@@ -3168,7 +3168,7 @@
         <v>00055F</v>
       </c>
     </row>
-    <row r="111" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="111" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B111" s="2">
         <v>87</v>
       </c>
@@ -3193,7 +3193,7 @@
         <v>00056F</v>
       </c>
     </row>
-    <row r="112" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="112" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B112" s="2">
         <v>88</v>
       </c>
@@ -3218,7 +3218,7 @@
         <v>00057F</v>
       </c>
     </row>
-    <row r="113" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="113" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B113" s="2">
         <v>89</v>
       </c>
@@ -3243,7 +3243,7 @@
         <v>00058F</v>
       </c>
     </row>
-    <row r="114" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="114" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B114" s="2">
         <v>90</v>
       </c>
@@ -3268,7 +3268,7 @@
         <v>00059F</v>
       </c>
     </row>
-    <row r="115" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="115" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B115" s="2">
         <v>91</v>
       </c>
@@ -3293,7 +3293,7 @@
         <v>0005AF</v>
       </c>
     </row>
-    <row r="116" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="116" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B116" s="2">
         <v>92</v>
       </c>
@@ -3318,7 +3318,7 @@
         <v>0005BF</v>
       </c>
     </row>
-    <row r="117" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="117" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B117" s="2">
         <v>93</v>
       </c>
@@ -3343,7 +3343,7 @@
         <v>0005CF</v>
       </c>
     </row>
-    <row r="118" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="118" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B118" s="2">
         <v>94</v>
       </c>
@@ -3368,7 +3368,7 @@
         <v>0005DF</v>
       </c>
     </row>
-    <row r="119" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="119" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B119" s="2">
         <v>95</v>
       </c>
@@ -3393,7 +3393,7 @@
         <v>0005EF</v>
       </c>
     </row>
-    <row r="120" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="120" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B120" s="2">
         <v>96</v>
       </c>
@@ -3418,7 +3418,7 @@
         <v>0005FF</v>
       </c>
     </row>
-    <row r="121" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="121" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B121" s="2">
         <v>97</v>
       </c>
@@ -3443,7 +3443,7 @@
         <v>00060F</v>
       </c>
     </row>
-    <row r="122" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="122" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B122" s="2">
         <v>98</v>
       </c>
@@ -3468,7 +3468,7 @@
         <v>00061F</v>
       </c>
     </row>
-    <row r="123" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="123" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B123" s="2">
         <v>99</v>
       </c>
@@ -3493,7 +3493,7 @@
         <v>00062F</v>
       </c>
     </row>
-    <row r="124" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="124" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B124" s="2">
         <v>100</v>
       </c>
@@ -3518,7 +3518,7 @@
         <v>00063F</v>
       </c>
     </row>
-    <row r="125" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="125" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B125" s="2">
         <v>101</v>
       </c>
@@ -3543,7 +3543,7 @@
         <v>00064F</v>
       </c>
     </row>
-    <row r="126" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="126" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B126" s="2">
         <v>102</v>
       </c>
@@ -3568,7 +3568,7 @@
         <v>00065F</v>
       </c>
     </row>
-    <row r="127" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="127" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B127" s="2">
         <v>103</v>
       </c>
@@ -3593,7 +3593,7 @@
         <v>00066F</v>
       </c>
     </row>
-    <row r="128" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="128" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B128" s="2">
         <v>104</v>
       </c>
@@ -3618,7 +3618,7 @@
         <v>00067F</v>
       </c>
     </row>
-    <row r="129" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="129" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B129" s="2">
         <v>105</v>
       </c>
@@ -3643,7 +3643,7 @@
         <v>00068F</v>
       </c>
     </row>
-    <row r="130" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="130" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B130" s="2">
         <v>106</v>
       </c>
@@ -3668,7 +3668,7 @@
         <v>00069F</v>
       </c>
     </row>
-    <row r="131" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="131" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B131" s="2">
         <v>107</v>
       </c>
@@ -3693,7 +3693,7 @@
         <v>0006AF</v>
       </c>
     </row>
-    <row r="132" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="132" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B132" s="2">
         <v>108</v>
       </c>
@@ -3718,7 +3718,7 @@
         <v>0006BF</v>
       </c>
     </row>
-    <row r="133" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="133" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B133" s="2">
         <v>109</v>
       </c>
@@ -3743,7 +3743,7 @@
         <v>0006CF</v>
       </c>
     </row>
-    <row r="134" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="134" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B134" s="2">
         <v>110</v>
       </c>
@@ -3768,7 +3768,7 @@
         <v>0006DF</v>
       </c>
     </row>
-    <row r="135" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="135" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B135" s="2">
         <v>111</v>
       </c>
@@ -3793,7 +3793,7 @@
         <v>0006EF</v>
       </c>
     </row>
-    <row r="136" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="136" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B136" s="2">
         <v>112</v>
       </c>
@@ -3818,7 +3818,7 @@
         <v>0006FF</v>
       </c>
     </row>
-    <row r="137" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="137" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B137" s="2">
         <v>113</v>
       </c>
@@ -3843,7 +3843,7 @@
         <v>00070F</v>
       </c>
     </row>
-    <row r="138" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="138" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B138" s="2">
         <v>114</v>
       </c>
@@ -3868,7 +3868,7 @@
         <v>00071F</v>
       </c>
     </row>
-    <row r="139" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="139" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B139" s="2">
         <v>115</v>
       </c>
@@ -3893,7 +3893,7 @@
         <v>00072F</v>
       </c>
     </row>
-    <row r="140" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="140" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B140" s="2">
         <v>116</v>
       </c>
@@ -3918,7 +3918,7 @@
         <v>00073F</v>
       </c>
     </row>
-    <row r="141" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="141" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B141" s="2">
         <v>117</v>
       </c>
@@ -3943,7 +3943,7 @@
         <v>00074F</v>
       </c>
     </row>
-    <row r="142" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="142" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B142" s="2">
         <v>118</v>
       </c>
@@ -3968,7 +3968,7 @@
         <v>00075F</v>
       </c>
     </row>
-    <row r="143" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="143" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B143" s="2">
         <v>119</v>
       </c>
@@ -3993,7 +3993,7 @@
         <v>00076F</v>
       </c>
     </row>
-    <row r="144" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="144" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B144" s="2">
         <v>120</v>
       </c>
@@ -4018,7 +4018,7 @@
         <v>00077F</v>
       </c>
     </row>
-    <row r="145" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="145" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B145" s="2">
         <v>121</v>
       </c>
@@ -4043,7 +4043,7 @@
         <v>00078F</v>
       </c>
     </row>
-    <row r="146" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="146" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B146" s="2">
         <v>122</v>
       </c>
@@ -4068,7 +4068,7 @@
         <v>00079F</v>
       </c>
     </row>
-    <row r="147" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="147" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B147" s="2">
         <v>123</v>
       </c>
@@ -4093,7 +4093,7 @@
         <v>0007AF</v>
       </c>
     </row>
-    <row r="148" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="148" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B148" s="2">
         <v>124</v>
       </c>
@@ -4118,7 +4118,7 @@
         <v>0007BF</v>
       </c>
     </row>
-    <row r="149" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="149" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B149" s="2">
         <v>125</v>
       </c>
@@ -4143,7 +4143,7 @@
         <v>0007CF</v>
       </c>
     </row>
-    <row r="150" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="150" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B150" s="2">
         <v>126</v>
       </c>
@@ -4168,7 +4168,7 @@
         <v>0007DF</v>
       </c>
     </row>
-    <row r="151" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="151" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B151" s="2">
         <v>127</v>
       </c>
@@ -4193,7 +4193,7 @@
         <v>0007EF</v>
       </c>
     </row>
-    <row r="152" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="152" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B152" s="2">
         <v>128</v>
       </c>
@@ -4218,7 +4218,7 @@
         <v>0007FF</v>
       </c>
     </row>
-    <row r="153" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="153" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B153" s="2">
         <v>129</v>
       </c>
@@ -4243,7 +4243,7 @@
         <v>00080F</v>
       </c>
     </row>
-    <row r="154" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="154" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B154" s="2">
         <v>130</v>
       </c>
@@ -4268,7 +4268,7 @@
         <v>00081F</v>
       </c>
     </row>
-    <row r="155" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="155" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B155" s="2">
         <v>131</v>
       </c>
@@ -4293,7 +4293,7 @@
         <v>00082F</v>
       </c>
     </row>
-    <row r="156" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="156" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B156" s="2">
         <v>132</v>
       </c>
@@ -4318,7 +4318,7 @@
         <v>00083F</v>
       </c>
     </row>
-    <row r="157" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="157" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B157" s="2">
         <v>133</v>
       </c>
@@ -4343,7 +4343,7 @@
         <v>00084F</v>
       </c>
     </row>
-    <row r="158" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="158" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B158" s="2">
         <v>134</v>
       </c>
@@ -4368,7 +4368,7 @@
         <v>00085F</v>
       </c>
     </row>
-    <row r="159" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="159" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B159" s="2">
         <v>135</v>
       </c>
@@ -4393,7 +4393,7 @@
         <v>00086F</v>
       </c>
     </row>
-    <row r="160" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="160" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B160" s="2">
         <v>136</v>
       </c>
@@ -4418,7 +4418,7 @@
         <v>00087F</v>
       </c>
     </row>
-    <row r="161" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="161" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B161" s="2">
         <v>137</v>
       </c>
@@ -4443,7 +4443,7 @@
         <v>00088F</v>
       </c>
     </row>
-    <row r="162" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="162" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B162" s="2">
         <v>138</v>
       </c>
@@ -4468,7 +4468,7 @@
         <v>00089F</v>
       </c>
     </row>
-    <row r="163" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="163" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B163" s="2">
         <v>139</v>
       </c>
@@ -4493,7 +4493,7 @@
         <v>0008AF</v>
       </c>
     </row>
-    <row r="164" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="164" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B164" s="2">
         <v>140</v>
       </c>
@@ -4518,7 +4518,7 @@
         <v>0008BF</v>
       </c>
     </row>
-    <row r="165" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="165" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B165" s="2">
         <v>141</v>
       </c>
@@ -4543,7 +4543,7 @@
         <v>0008CF</v>
       </c>
     </row>
-    <row r="166" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="166" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B166" s="2">
         <v>142</v>
       </c>
@@ -4568,7 +4568,7 @@
         <v>0008DF</v>
       </c>
     </row>
-    <row r="167" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="167" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B167" s="2">
         <v>143</v>
       </c>
@@ -4593,7 +4593,7 @@
         <v>0008EF</v>
       </c>
     </row>
-    <row r="168" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="168" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B168" s="2">
         <v>144</v>
       </c>
@@ -4618,7 +4618,7 @@
         <v>0008FF</v>
       </c>
     </row>
-    <row r="169" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="169" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B169" s="2">
         <v>145</v>
       </c>
@@ -4643,7 +4643,7 @@
         <v>00090F</v>
       </c>
     </row>
-    <row r="170" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="170" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B170" s="2">
         <v>146</v>
       </c>
@@ -4668,7 +4668,7 @@
         <v>00091F</v>
       </c>
     </row>
-    <row r="171" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="171" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B171" s="2">
         <v>147</v>
       </c>
@@ -4693,7 +4693,7 @@
         <v>00092F</v>
       </c>
     </row>
-    <row r="172" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="172" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B172" s="2">
         <v>148</v>
       </c>
@@ -4718,7 +4718,7 @@
         <v>00093F</v>
       </c>
     </row>
-    <row r="173" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="173" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B173" s="2">
         <v>149</v>
       </c>
@@ -4743,7 +4743,7 @@
         <v>00094F</v>
       </c>
     </row>
-    <row r="174" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="174" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B174" s="2">
         <v>150</v>
       </c>
@@ -4768,7 +4768,7 @@
         <v>00095F</v>
       </c>
     </row>
-    <row r="175" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="175" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B175" s="2">
         <v>151</v>
       </c>
@@ -4793,7 +4793,7 @@
         <v>00096F</v>
       </c>
     </row>
-    <row r="176" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="176" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B176" s="2">
         <v>152</v>
       </c>
@@ -4818,7 +4818,7 @@
         <v>00097F</v>
       </c>
     </row>
-    <row r="177" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="177" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B177" s="2">
         <v>153</v>
       </c>
@@ -4843,7 +4843,7 @@
         <v>00098F</v>
       </c>
     </row>
-    <row r="178" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="178" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B178" s="2">
         <v>154</v>
       </c>
@@ -4868,7 +4868,7 @@
         <v>00099F</v>
       </c>
     </row>
-    <row r="179" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="179" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B179" s="2">
         <v>155</v>
       </c>
@@ -4893,7 +4893,7 @@
         <v>0009AF</v>
       </c>
     </row>
-    <row r="180" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="180" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B180" s="2">
         <v>156</v>
       </c>
@@ -4918,7 +4918,7 @@
         <v>0009BF</v>
       </c>
     </row>
-    <row r="181" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="181" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B181" s="2">
         <v>157</v>
       </c>
@@ -4943,7 +4943,7 @@
         <v>0009CF</v>
       </c>
     </row>
-    <row r="182" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="182" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B182" s="2">
         <v>158</v>
       </c>
@@ -4968,7 +4968,7 @@
         <v>0009DF</v>
       </c>
     </row>
-    <row r="183" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="183" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B183" s="2">
         <v>159</v>
       </c>
@@ -4993,7 +4993,7 @@
         <v>0009EF</v>
       </c>
     </row>
-    <row r="184" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="184" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B184" s="2">
         <v>160</v>
       </c>
@@ -5018,7 +5018,7 @@
         <v>0009FF</v>
       </c>
     </row>
-    <row r="185" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="185" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B185" s="2">
         <v>161</v>
       </c>
@@ -5043,7 +5043,7 @@
         <v>000A0F</v>
       </c>
     </row>
-    <row r="186" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="186" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B186" s="2">
         <v>162</v>
       </c>
@@ -5068,7 +5068,7 @@
         <v>000A1F</v>
       </c>
     </row>
-    <row r="187" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="187" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B187" s="2">
         <v>163</v>
       </c>
@@ -5093,7 +5093,7 @@
         <v>000A2F</v>
       </c>
     </row>
-    <row r="188" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="188" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B188" s="2">
         <v>164</v>
       </c>
@@ -5118,7 +5118,7 @@
         <v>000A3F</v>
       </c>
     </row>
-    <row r="189" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="189" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B189" s="2">
         <v>165</v>
       </c>
@@ -5143,7 +5143,7 @@
         <v>000A4F</v>
       </c>
     </row>
-    <row r="190" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="190" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B190" s="2">
         <v>166</v>
       </c>
@@ -5168,7 +5168,7 @@
         <v>000A5F</v>
       </c>
     </row>
-    <row r="191" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="191" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B191" s="2">
         <v>167</v>
       </c>
@@ -5193,7 +5193,7 @@
         <v>000A6F</v>
       </c>
     </row>
-    <row r="192" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="192" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B192" s="2">
         <v>168</v>
       </c>
@@ -5218,7 +5218,7 @@
         <v>000A7F</v>
       </c>
     </row>
-    <row r="193" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="193" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B193" s="2">
         <v>169</v>
       </c>
@@ -5243,7 +5243,7 @@
         <v>000A8F</v>
       </c>
     </row>
-    <row r="194" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="194" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B194" s="2">
         <v>170</v>
       </c>
@@ -5268,7 +5268,7 @@
         <v>000A9F</v>
       </c>
     </row>
-    <row r="195" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="195" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B195" s="2">
         <v>171</v>
       </c>
@@ -5293,7 +5293,7 @@
         <v>000AAF</v>
       </c>
     </row>
-    <row r="196" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="196" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B196" s="2">
         <v>172</v>
       </c>
@@ -5318,7 +5318,7 @@
         <v>000ABF</v>
       </c>
     </row>
-    <row r="197" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="197" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B197" s="2">
         <v>173</v>
       </c>
@@ -5343,7 +5343,7 @@
         <v>000ACF</v>
       </c>
     </row>
-    <row r="198" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="198" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B198" s="2">
         <v>174</v>
       </c>
@@ -5368,7 +5368,7 @@
         <v>000ADF</v>
       </c>
     </row>
-    <row r="199" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="199" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B199" s="2">
         <v>175</v>
       </c>
@@ -5393,7 +5393,7 @@
         <v>000AEF</v>
       </c>
     </row>
-    <row r="200" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="200" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B200" s="2">
         <v>176</v>
       </c>
@@ -5418,7 +5418,7 @@
         <v>000AFF</v>
       </c>
     </row>
-    <row r="201" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="201" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B201" s="2">
         <v>177</v>
       </c>
@@ -5443,7 +5443,7 @@
         <v>000B0F</v>
       </c>
     </row>
-    <row r="202" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="202" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B202" s="2">
         <v>178</v>
       </c>
@@ -5468,7 +5468,7 @@
         <v>000B1F</v>
       </c>
     </row>
-    <row r="203" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="203" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B203" s="2">
         <v>179</v>
       </c>
@@ -5493,7 +5493,7 @@
         <v>000B2F</v>
       </c>
     </row>
-    <row r="204" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="204" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B204" s="2">
         <v>180</v>
       </c>
@@ -5518,7 +5518,7 @@
         <v>000B3F</v>
       </c>
     </row>
-    <row r="205" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="205" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B205" s="2">
         <v>181</v>
       </c>
@@ -5543,7 +5543,7 @@
         <v>000B4F</v>
       </c>
     </row>
-    <row r="206" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="206" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B206" s="2">
         <v>182</v>
       </c>
@@ -5568,7 +5568,7 @@
         <v>000B5F</v>
       </c>
     </row>
-    <row r="207" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="207" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B207" s="2">
         <v>183</v>
       </c>
@@ -5593,7 +5593,7 @@
         <v>000B6F</v>
       </c>
     </row>
-    <row r="208" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="208" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B208" s="2">
         <v>184</v>
       </c>
@@ -5618,7 +5618,7 @@
         <v>000B7F</v>
       </c>
     </row>
-    <row r="209" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="209" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B209" s="2">
         <v>185</v>
       </c>
@@ -5643,7 +5643,7 @@
         <v>000B8F</v>
       </c>
     </row>
-    <row r="210" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="210" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B210" s="2">
         <v>186</v>
       </c>
@@ -5668,7 +5668,7 @@
         <v>000B9F</v>
       </c>
     </row>
-    <row r="211" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="211" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B211" s="2">
         <v>187</v>
       </c>
@@ -5693,7 +5693,7 @@
         <v>000BAF</v>
       </c>
     </row>
-    <row r="212" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="212" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B212" s="2">
         <v>188</v>
       </c>
@@ -5718,7 +5718,7 @@
         <v>000BBF</v>
       </c>
     </row>
-    <row r="213" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="213" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B213" s="2">
         <v>189</v>
       </c>
@@ -5743,7 +5743,7 @@
         <v>000BCF</v>
       </c>
     </row>
-    <row r="214" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="214" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B214" s="2">
         <v>190</v>
       </c>
@@ -5768,7 +5768,7 @@
         <v>000BDF</v>
       </c>
     </row>
-    <row r="215" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="215" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B215" s="2">
         <v>191</v>
       </c>
@@ -5793,7 +5793,7 @@
         <v>000BEF</v>
       </c>
     </row>
-    <row r="216" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="216" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B216" s="2">
         <v>192</v>
       </c>
@@ -5818,7 +5818,7 @@
         <v>000BFF</v>
       </c>
     </row>
-    <row r="217" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="217" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B217" s="2">
         <v>193</v>
       </c>
@@ -5843,7 +5843,7 @@
         <v>000C0F</v>
       </c>
     </row>
-    <row r="218" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="218" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B218" s="2">
         <v>194</v>
       </c>
@@ -5868,7 +5868,7 @@
         <v>000C1F</v>
       </c>
     </row>
-    <row r="219" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="219" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B219" s="2">
         <v>195</v>
       </c>
@@ -5893,7 +5893,7 @@
         <v>000C2F</v>
       </c>
     </row>
-    <row r="220" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="220" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B220" s="2">
         <v>196</v>
       </c>
@@ -5918,7 +5918,7 @@
         <v>000C3F</v>
       </c>
     </row>
-    <row r="221" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="221" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B221" s="2">
         <v>197</v>
       </c>
@@ -5943,7 +5943,7 @@
         <v>000C4F</v>
       </c>
     </row>
-    <row r="222" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="222" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B222" s="2">
         <v>198</v>
       </c>
@@ -5968,7 +5968,7 @@
         <v>000C5F</v>
       </c>
     </row>
-    <row r="223" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="223" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B223" s="2">
         <v>199</v>
       </c>
@@ -5993,7 +5993,7 @@
         <v>000C6F</v>
       </c>
     </row>
-    <row r="224" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="224" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B224" s="2">
         <v>200</v>
       </c>
@@ -6018,7 +6018,7 @@
         <v>000C7F</v>
       </c>
     </row>
-    <row r="225" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="225" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B225" s="2">
         <v>201</v>
       </c>
@@ -6043,7 +6043,7 @@
         <v>000C8F</v>
       </c>
     </row>
-    <row r="226" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="226" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B226" s="2">
         <v>202</v>
       </c>
@@ -6068,7 +6068,7 @@
         <v>000C9F</v>
       </c>
     </row>
-    <row r="227" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="227" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B227" s="2">
         <v>203</v>
       </c>
@@ -6093,7 +6093,7 @@
         <v>000CAF</v>
       </c>
     </row>
-    <row r="228" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="228" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B228" s="2">
         <v>204</v>
       </c>
@@ -6118,7 +6118,7 @@
         <v>000CBF</v>
       </c>
     </row>
-    <row r="229" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="229" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B229" s="2">
         <v>205</v>
       </c>
@@ -6143,7 +6143,7 @@
         <v>000CCF</v>
       </c>
     </row>
-    <row r="230" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="230" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B230" s="2">
         <v>206</v>
       </c>
@@ -6168,7 +6168,7 @@
         <v>000CDF</v>
       </c>
     </row>
-    <row r="231" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="231" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B231" s="2">
         <v>207</v>
       </c>
@@ -6193,7 +6193,7 @@
         <v>000CEF</v>
       </c>
     </row>
-    <row r="232" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="232" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B232" s="2">
         <v>208</v>
       </c>
@@ -6218,7 +6218,7 @@
         <v>000CFF</v>
       </c>
     </row>
-    <row r="233" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="233" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B233" s="2">
         <v>209</v>
       </c>
@@ -6243,7 +6243,7 @@
         <v>000D0F</v>
       </c>
     </row>
-    <row r="234" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="234" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B234" s="2">
         <v>210</v>
       </c>
@@ -6268,7 +6268,7 @@
         <v>000D1F</v>
       </c>
     </row>
-    <row r="235" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="235" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B235" s="2">
         <v>211</v>
       </c>
@@ -6293,7 +6293,7 @@
         <v>000D2F</v>
       </c>
     </row>
-    <row r="236" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="236" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B236" s="2">
         <v>212</v>
       </c>
@@ -6318,7 +6318,7 @@
         <v>000D3F</v>
       </c>
     </row>
-    <row r="237" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="237" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B237" s="2">
         <v>213</v>
       </c>
@@ -6343,7 +6343,7 @@
         <v>000D4F</v>
       </c>
     </row>
-    <row r="238" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="238" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B238" s="2">
         <v>214</v>
       </c>
@@ -6368,7 +6368,7 @@
         <v>000D5F</v>
       </c>
     </row>
-    <row r="239" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="239" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B239" s="2">
         <v>215</v>
       </c>
@@ -6393,7 +6393,7 @@
         <v>000D6F</v>
       </c>
     </row>
-    <row r="240" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="240" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B240" s="2">
         <v>216</v>
       </c>
@@ -6418,7 +6418,7 @@
         <v>000D7F</v>
       </c>
     </row>
-    <row r="241" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="241" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B241" s="2">
         <v>217</v>
       </c>
@@ -6443,7 +6443,7 @@
         <v>000D8F</v>
       </c>
     </row>
-    <row r="242" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="242" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B242" s="2">
         <v>218</v>
       </c>
@@ -6468,7 +6468,7 @@
         <v>000D9F</v>
       </c>
     </row>
-    <row r="243" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="243" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B243" s="2">
         <v>219</v>
       </c>
@@ -6493,7 +6493,7 @@
         <v>000DAF</v>
       </c>
     </row>
-    <row r="244" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="244" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B244" s="2">
         <v>220</v>
       </c>
@@ -6518,7 +6518,7 @@
         <v>000DBF</v>
       </c>
     </row>
-    <row r="245" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="245" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B245" s="2">
         <v>221</v>
       </c>
@@ -6543,7 +6543,7 @@
         <v>000DCF</v>
       </c>
     </row>
-    <row r="246" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="246" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B246" s="2">
         <v>222</v>
       </c>
@@ -6568,7 +6568,7 @@
         <v>000DDF</v>
       </c>
     </row>
-    <row r="247" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="247" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B247" s="2">
         <v>223</v>
       </c>
@@ -6593,7 +6593,7 @@
         <v>000DEF</v>
       </c>
     </row>
-    <row r="248" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="248" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B248" s="2">
         <v>224</v>
       </c>
@@ -6618,7 +6618,7 @@
         <v>000DFF</v>
       </c>
     </row>
-    <row r="249" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="249" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B249" s="2">
         <v>225</v>
       </c>
@@ -6643,7 +6643,7 @@
         <v>000E0F</v>
       </c>
     </row>
-    <row r="250" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="250" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B250" s="2">
         <v>226</v>
       </c>
@@ -6668,7 +6668,7 @@
         <v>000E1F</v>
       </c>
     </row>
-    <row r="251" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="251" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B251" s="2">
         <v>227</v>
       </c>
@@ -6693,7 +6693,7 @@
         <v>000E2F</v>
       </c>
     </row>
-    <row r="252" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="252" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B252" s="2">
         <v>228</v>
       </c>
@@ -6718,7 +6718,7 @@
         <v>000E3F</v>
       </c>
     </row>
-    <row r="253" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="253" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B253" s="2">
         <v>229</v>
       </c>
@@ -6743,7 +6743,7 @@
         <v>000E4F</v>
       </c>
     </row>
-    <row r="254" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="254" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B254" s="2">
         <v>230</v>
       </c>
@@ -6768,7 +6768,7 @@
         <v>000E5F</v>
       </c>
     </row>
-    <row r="255" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="255" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B255" s="2">
         <v>231</v>
       </c>
@@ -6793,7 +6793,7 @@
         <v>000E6F</v>
       </c>
     </row>
-    <row r="256" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="256" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B256" s="2">
         <v>232</v>
       </c>
@@ -6818,7 +6818,7 @@
         <v>000E7F</v>
       </c>
     </row>
-    <row r="257" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="257" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B257" s="2">
         <v>233</v>
       </c>
@@ -6843,7 +6843,7 @@
         <v>000E8F</v>
       </c>
     </row>
-    <row r="258" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="258" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B258" s="2">
         <v>234</v>
       </c>
@@ -6868,7 +6868,7 @@
         <v>000E9F</v>
       </c>
     </row>
-    <row r="259" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="259" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B259" s="2">
         <v>235</v>
       </c>
@@ -6893,7 +6893,7 @@
         <v>000EAF</v>
       </c>
     </row>
-    <row r="260" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="260" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B260" s="2">
         <v>236</v>
       </c>
@@ -6918,7 +6918,7 @@
         <v>000EBF</v>
       </c>
     </row>
-    <row r="261" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="261" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B261" s="2">
         <v>237</v>
       </c>
@@ -6943,7 +6943,7 @@
         <v>000ECF</v>
       </c>
     </row>
-    <row r="262" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="262" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B262" s="2">
         <v>238</v>
       </c>
@@ -6968,7 +6968,7 @@
         <v>000EDF</v>
       </c>
     </row>
-    <row r="263" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="263" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B263" s="2">
         <v>239</v>
       </c>
@@ -6993,7 +6993,7 @@
         <v>000EEF</v>
       </c>
     </row>
-    <row r="264" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="264" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B264" s="2">
         <v>240</v>
       </c>
@@ -7018,7 +7018,7 @@
         <v>000EFF</v>
       </c>
     </row>
-    <row r="265" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="265" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B265" s="2">
         <v>241</v>
       </c>
@@ -7043,7 +7043,7 @@
         <v>000F0F</v>
       </c>
     </row>
-    <row r="266" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="266" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B266" s="2">
         <v>242</v>
       </c>
@@ -7068,7 +7068,7 @@
         <v>000F1F</v>
       </c>
     </row>
-    <row r="267" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="267" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B267" s="2">
         <v>243</v>
       </c>
@@ -7093,7 +7093,7 @@
         <v>000F2F</v>
       </c>
     </row>
-    <row r="268" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="268" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B268" s="2">
         <v>244</v>
       </c>
@@ -7118,7 +7118,7 @@
         <v>000F3F</v>
       </c>
     </row>
-    <row r="269" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="269" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B269" s="2">
         <v>245</v>
       </c>
@@ -7143,7 +7143,7 @@
         <v>000F4F</v>
       </c>
     </row>
-    <row r="270" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="270" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B270" s="2">
         <v>246</v>
       </c>
@@ -7168,7 +7168,7 @@
         <v>000F5F</v>
       </c>
     </row>
-    <row r="271" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="271" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B271" s="2">
         <v>247</v>
       </c>
@@ -7193,7 +7193,7 @@
         <v>000F6F</v>
       </c>
     </row>
-    <row r="272" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="272" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B272" s="2">
         <v>248</v>
       </c>
@@ -7218,7 +7218,7 @@
         <v>000F7F</v>
       </c>
     </row>
-    <row r="273" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="273" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B273" s="2">
         <v>249</v>
       </c>
@@ -7243,7 +7243,7 @@
         <v>000F8F</v>
       </c>
     </row>
-    <row r="274" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="274" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B274" s="2">
         <v>250</v>
       </c>
@@ -7268,7 +7268,7 @@
         <v>000F9F</v>
       </c>
     </row>
-    <row r="275" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="275" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B275" s="2">
         <v>251</v>
       </c>
@@ -7293,7 +7293,7 @@
         <v>000FAF</v>
       </c>
     </row>
-    <row r="276" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="276" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B276" s="2">
         <v>252</v>
       </c>
@@ -7318,7 +7318,7 @@
         <v>000FBF</v>
       </c>
     </row>
-    <row r="277" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="277" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B277" s="2">
         <v>253</v>
       </c>
@@ -7343,7 +7343,7 @@
         <v>000FCF</v>
       </c>
     </row>
-    <row r="278" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="278" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B278" s="2">
         <v>254</v>
       </c>
@@ -7368,7 +7368,7 @@
         <v>000FDF</v>
       </c>
     </row>
-    <row r="279" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="279" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B279" s="2">
         <v>255</v>
       </c>
@@ -7393,7 +7393,7 @@
         <v>000FEF</v>
       </c>
     </row>
-    <row r="280" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="280" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B280" s="2">
         <v>256</v>
       </c>
@@ -7406,7 +7406,7 @@
         <v>000FFF</v>
       </c>
     </row>
-    <row r="281" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="281" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B281" s="2">
         <v>257</v>
       </c>
@@ -7419,7 +7419,7 @@
         <v>00100F</v>
       </c>
     </row>
-    <row r="282" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="282" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B282" s="2">
         <v>258</v>
       </c>
@@ -7432,7 +7432,7 @@
         <v>00101F</v>
       </c>
     </row>
-    <row r="283" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="283" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B283" s="2">
         <v>259</v>
       </c>
@@ -7445,7 +7445,7 @@
         <v>00102F</v>
       </c>
     </row>
-    <row r="284" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="284" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B284" s="2">
         <v>260</v>
       </c>
@@ -7458,7 +7458,7 @@
         <v>00103F</v>
       </c>
     </row>
-    <row r="285" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="285" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B285" s="2">
         <v>261</v>
       </c>
@@ -7471,7 +7471,7 @@
         <v>00104F</v>
       </c>
     </row>
-    <row r="286" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="286" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B286" s="2">
         <v>262</v>
       </c>
@@ -7484,7 +7484,7 @@
         <v>00105F</v>
       </c>
     </row>
-    <row r="287" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="287" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B287" s="2">
         <v>263</v>
       </c>
@@ -7497,7 +7497,7 @@
         <v>00106F</v>
       </c>
     </row>
-    <row r="288" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="288" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B288" s="2">
         <v>264</v>
       </c>
@@ -7510,7 +7510,7 @@
         <v>00107F</v>
       </c>
     </row>
-    <row r="289" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="289" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B289" s="2">
         <v>265</v>
       </c>
@@ -7523,7 +7523,7 @@
         <v>00108F</v>
       </c>
     </row>
-    <row r="290" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="290" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B290" s="2">
         <v>266</v>
       </c>
@@ -7536,7 +7536,7 @@
         <v>00109F</v>
       </c>
     </row>
-    <row r="291" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="291" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B291" s="2">
         <v>267</v>
       </c>
@@ -7549,7 +7549,7 @@
         <v>0010AF</v>
       </c>
     </row>
-    <row r="292" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="292" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B292" s="2">
         <v>268</v>
       </c>
@@ -7562,7 +7562,7 @@
         <v>0010BF</v>
       </c>
     </row>
-    <row r="293" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="293" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B293" s="2">
         <v>269</v>
       </c>
@@ -7575,7 +7575,7 @@
         <v>0010CF</v>
       </c>
     </row>
-    <row r="294" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="294" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B294" s="2">
         <v>270</v>
       </c>
@@ -7588,7 +7588,7 @@
         <v>0010DF</v>
       </c>
     </row>
-    <row r="295" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="295" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B295" s="2">
         <v>271</v>
       </c>
@@ -7601,7 +7601,7 @@
         <v>0010EF</v>
       </c>
     </row>
-    <row r="296" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="296" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B296" s="2">
         <v>272</v>
       </c>
@@ -7614,7 +7614,7 @@
         <v>0010FF</v>
       </c>
     </row>
-    <row r="297" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="297" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B297" s="2">
         <v>273</v>
       </c>
@@ -7627,7 +7627,7 @@
         <v>00110F</v>
       </c>
     </row>
-    <row r="298" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="298" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B298" s="2">
         <v>274</v>
       </c>
@@ -7640,7 +7640,7 @@
         <v>00111F</v>
       </c>
     </row>
-    <row r="299" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="299" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B299" s="2">
         <v>275</v>
       </c>
@@ -7653,7 +7653,7 @@
         <v>00112F</v>
       </c>
     </row>
-    <row r="300" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="300" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B300" s="2">
         <v>276</v>
       </c>
@@ -7666,7 +7666,7 @@
         <v>00113F</v>
       </c>
     </row>
-    <row r="301" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="301" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B301" s="2">
         <v>277</v>
       </c>
@@ -7679,7 +7679,7 @@
         <v>00114F</v>
       </c>
     </row>
-    <row r="302" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="302" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B302" s="2">
         <v>278</v>
       </c>
@@ -7692,7 +7692,7 @@
         <v>00115F</v>
       </c>
     </row>
-    <row r="303" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="303" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B303" s="2">
         <v>279</v>
       </c>
@@ -7705,7 +7705,7 @@
         <v>00116F</v>
       </c>
     </row>
-    <row r="304" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="304" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B304" s="2">
         <v>280</v>
       </c>
@@ -7718,7 +7718,7 @@
         <v>00117F</v>
       </c>
     </row>
-    <row r="305" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="305" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B305" s="2">
         <v>281</v>
       </c>
@@ -7731,7 +7731,7 @@
         <v>00118F</v>
       </c>
     </row>
-    <row r="306" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="306" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B306" s="2">
         <v>282</v>
       </c>
@@ -7744,7 +7744,7 @@
         <v>00119F</v>
       </c>
     </row>
-    <row r="307" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="307" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B307" s="2">
         <v>283</v>
       </c>
@@ -7757,7 +7757,7 @@
         <v>0011AF</v>
       </c>
     </row>
-    <row r="308" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="308" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B308" s="2">
         <v>284</v>
       </c>
@@ -7770,7 +7770,7 @@
         <v>0011BF</v>
       </c>
     </row>
-    <row r="309" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="309" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B309" s="2">
         <v>285</v>
       </c>
@@ -7783,7 +7783,7 @@
         <v>0011CF</v>
       </c>
     </row>
-    <row r="310" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="310" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B310" s="2">
         <v>286</v>
       </c>
@@ -7796,7 +7796,7 @@
         <v>0011DF</v>
       </c>
     </row>
-    <row r="311" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="311" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B311" s="2">
         <v>287</v>
       </c>
@@ -7809,7 +7809,7 @@
         <v>0011EF</v>
       </c>
     </row>
-    <row r="312" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="312" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B312" s="2">
         <v>288</v>
       </c>
@@ -7822,7 +7822,7 @@
         <v>0011FF</v>
       </c>
     </row>
-    <row r="313" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="313" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B313" s="2">
         <v>289</v>
       </c>
@@ -7835,7 +7835,7 @@
         <v>00120F</v>
       </c>
     </row>
-    <row r="314" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="314" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B314" s="2">
         <v>290</v>
       </c>
@@ -7848,7 +7848,7 @@
         <v>00121F</v>
       </c>
     </row>
-    <row r="315" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="315" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B315" s="2">
         <v>291</v>
       </c>
@@ -7861,7 +7861,7 @@
         <v>00122F</v>
       </c>
     </row>
-    <row r="316" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="316" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B316" s="2">
         <v>292</v>
       </c>
@@ -7874,7 +7874,7 @@
         <v>00123F</v>
       </c>
     </row>
-    <row r="317" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="317" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B317" s="2">
         <v>293</v>
       </c>
@@ -7887,7 +7887,7 @@
         <v>00124F</v>
       </c>
     </row>
-    <row r="318" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="318" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B318" s="2">
         <v>294</v>
       </c>
@@ -7900,7 +7900,7 @@
         <v>00125F</v>
       </c>
     </row>
-    <row r="319" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="319" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B319" s="2">
         <v>295</v>
       </c>
@@ -7913,7 +7913,7 @@
         <v>00126F</v>
       </c>
     </row>
-    <row r="320" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="320" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B320" s="2">
         <v>296</v>
       </c>
@@ -7926,7 +7926,7 @@
         <v>00127F</v>
       </c>
     </row>
-    <row r="321" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="321" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B321" s="2">
         <v>297</v>
       </c>
@@ -7939,7 +7939,7 @@
         <v>00128F</v>
       </c>
     </row>
-    <row r="322" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="322" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B322" s="2">
         <v>298</v>
       </c>
@@ -7952,7 +7952,7 @@
         <v>00129F</v>
       </c>
     </row>
-    <row r="323" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="323" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B323" s="2">
         <v>299</v>
       </c>
@@ -7965,7 +7965,7 @@
         <v>0012AF</v>
       </c>
     </row>
-    <row r="324" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="324" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B324" s="2">
         <v>300</v>
       </c>
@@ -7978,7 +7978,7 @@
         <v>0012BF</v>
       </c>
     </row>
-    <row r="325" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="325" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B325" s="2">
         <v>301</v>
       </c>
@@ -7991,7 +7991,7 @@
         <v>0012CF</v>
       </c>
     </row>
-    <row r="326" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="326" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B326" s="2">
         <v>302</v>
       </c>
@@ -8004,7 +8004,7 @@
         <v>0012DF</v>
       </c>
     </row>
-    <row r="327" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="327" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B327" s="2">
         <v>303</v>
       </c>
@@ -8017,7 +8017,7 @@
         <v>0012EF</v>
       </c>
     </row>
-    <row r="328" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="328" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B328" s="2">
         <v>304</v>
       </c>
@@ -8030,7 +8030,7 @@
         <v>0012FF</v>
       </c>
     </row>
-    <row r="329" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="329" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B329" s="2">
         <v>305</v>
       </c>
@@ -8043,7 +8043,7 @@
         <v>00130F</v>
       </c>
     </row>
-    <row r="330" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="330" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B330" s="2">
         <v>306</v>
       </c>
@@ -8056,7 +8056,7 @@
         <v>00131F</v>
       </c>
     </row>
-    <row r="331" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="331" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B331" s="2">
         <v>307</v>
       </c>
@@ -8069,7 +8069,7 @@
         <v>00132F</v>
       </c>
     </row>
-    <row r="332" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="332" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B332" s="2">
         <v>308</v>
       </c>
@@ -8082,7 +8082,7 @@
         <v>00133F</v>
       </c>
     </row>
-    <row r="333" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="333" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B333" s="2">
         <v>309</v>
       </c>
@@ -8095,7 +8095,7 @@
         <v>00134F</v>
       </c>
     </row>
-    <row r="334" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="334" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B334" s="2">
         <v>310</v>
       </c>
@@ -8108,7 +8108,7 @@
         <v>00135F</v>
       </c>
     </row>
-    <row r="335" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="335" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B335" s="2">
         <v>311</v>
       </c>
@@ -8121,7 +8121,7 @@
         <v>00136F</v>
       </c>
     </row>
-    <row r="336" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="336" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B336" s="2">
         <v>312</v>
       </c>
@@ -8134,7 +8134,7 @@
         <v>00137F</v>
       </c>
     </row>
-    <row r="337" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="337" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B337" s="2">
         <v>313</v>
       </c>
@@ -8147,7 +8147,7 @@
         <v>00138F</v>
       </c>
     </row>
-    <row r="338" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="338" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B338" s="2">
         <v>314</v>
       </c>
@@ -8160,7 +8160,7 @@
         <v>00139F</v>
       </c>
     </row>
-    <row r="339" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="339" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B339" s="2">
         <v>315</v>
       </c>
@@ -8173,7 +8173,7 @@
         <v>0013AF</v>
       </c>
     </row>
-    <row r="340" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="340" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B340" s="2">
         <v>316</v>
       </c>
@@ -8186,7 +8186,7 @@
         <v>0013BF</v>
       </c>
     </row>
-    <row r="341" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="341" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B341" s="2">
         <v>317</v>
       </c>
@@ -8199,7 +8199,7 @@
         <v>0013CF</v>
       </c>
     </row>
-    <row r="342" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="342" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B342" s="2">
         <v>318</v>
       </c>
@@ -8212,7 +8212,7 @@
         <v>0013DF</v>
       </c>
     </row>
-    <row r="343" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="343" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B343" s="2">
         <v>319</v>
       </c>
@@ -8225,7 +8225,7 @@
         <v>0013EF</v>
       </c>
     </row>
-    <row r="344" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="344" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B344" s="2">
         <v>320</v>
       </c>
@@ -8238,7 +8238,7 @@
         <v>0013FF</v>
       </c>
     </row>
-    <row r="345" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="345" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B345" s="2">
         <v>321</v>
       </c>
@@ -8251,7 +8251,7 @@
         <v>00140F</v>
       </c>
     </row>
-    <row r="346" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="346" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B346" s="2">
         <v>322</v>
       </c>
@@ -8264,7 +8264,7 @@
         <v>00141F</v>
       </c>
     </row>
-    <row r="347" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="347" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B347" s="2">
         <v>323</v>
       </c>
@@ -8277,7 +8277,7 @@
         <v>00142F</v>
       </c>
     </row>
-    <row r="348" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="348" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B348" s="2">
         <v>324</v>
       </c>
@@ -8290,7 +8290,7 @@
         <v>00143F</v>
       </c>
     </row>
-    <row r="349" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="349" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B349" s="2">
         <v>325</v>
       </c>
@@ -8303,7 +8303,7 @@
         <v>00144F</v>
       </c>
     </row>
-    <row r="350" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="350" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B350" s="2">
         <v>326</v>
       </c>
@@ -8316,7 +8316,7 @@
         <v>00145F</v>
       </c>
     </row>
-    <row r="351" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="351" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B351" s="2">
         <v>327</v>
       </c>
@@ -8329,7 +8329,7 @@
         <v>00146F</v>
       </c>
     </row>
-    <row r="352" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="352" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B352" s="2">
         <v>328</v>
       </c>
@@ -8342,7 +8342,7 @@
         <v>00147F</v>
       </c>
     </row>
-    <row r="353" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="353" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B353" s="2">
         <v>329</v>
       </c>
@@ -8355,7 +8355,7 @@
         <v>00148F</v>
       </c>
     </row>
-    <row r="354" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="354" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B354" s="2">
         <v>330</v>
       </c>
@@ -8368,7 +8368,7 @@
         <v>00149F</v>
       </c>
     </row>
-    <row r="355" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="355" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B355" s="2">
         <v>331</v>
       </c>
@@ -8381,7 +8381,7 @@
         <v>0014AF</v>
       </c>
     </row>
-    <row r="356" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="356" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B356" s="2">
         <v>332</v>
       </c>
@@ -8394,7 +8394,7 @@
         <v>0014BF</v>
       </c>
     </row>
-    <row r="357" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="357" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B357" s="2">
         <v>333</v>
       </c>
@@ -8407,7 +8407,7 @@
         <v>0014CF</v>
       </c>
     </row>
-    <row r="358" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="358" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B358" s="2">
         <v>334</v>
       </c>
@@ -8420,7 +8420,7 @@
         <v>0014DF</v>
       </c>
     </row>
-    <row r="359" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="359" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B359" s="2">
         <v>335</v>
       </c>
@@ -8433,7 +8433,7 @@
         <v>0014EF</v>
       </c>
     </row>
-    <row r="360" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="360" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B360" s="2">
         <v>336</v>
       </c>
@@ -8446,7 +8446,7 @@
         <v>0014FF</v>
       </c>
     </row>
-    <row r="361" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="361" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B361" s="2">
         <v>337</v>
       </c>
@@ -8459,7 +8459,7 @@
         <v>00150F</v>
       </c>
     </row>
-    <row r="362" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="362" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B362" s="2">
         <v>338</v>
       </c>
@@ -8472,7 +8472,7 @@
         <v>00151F</v>
       </c>
     </row>
-    <row r="363" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="363" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B363" s="2">
         <v>339</v>
       </c>
@@ -8485,7 +8485,7 @@
         <v>00152F</v>
       </c>
     </row>
-    <row r="364" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="364" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B364" s="2">
         <v>340</v>
       </c>
@@ -8498,7 +8498,7 @@
         <v>00153F</v>
       </c>
     </row>
-    <row r="365" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="365" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B365" s="2">
         <v>341</v>
       </c>
@@ -8511,7 +8511,7 @@
         <v>00154F</v>
       </c>
     </row>
-    <row r="366" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="366" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B366" s="2">
         <v>342</v>
       </c>
@@ -8524,7 +8524,7 @@
         <v>00155F</v>
       </c>
     </row>
-    <row r="367" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="367" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B367" s="2">
         <v>343</v>
       </c>
@@ -8537,7 +8537,7 @@
         <v>00156F</v>
       </c>
     </row>
-    <row r="368" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="368" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B368" s="2">
         <v>344</v>
       </c>
@@ -8550,7 +8550,7 @@
         <v>00157F</v>
       </c>
     </row>
-    <row r="369" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="369" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B369" s="2">
         <v>345</v>
       </c>
@@ -8563,7 +8563,7 @@
         <v>00158F</v>
       </c>
     </row>
-    <row r="370" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="370" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B370" s="2">
         <v>346</v>
       </c>
@@ -8576,7 +8576,7 @@
         <v>00159F</v>
       </c>
     </row>
-    <row r="371" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="371" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B371" s="2">
         <v>347</v>
       </c>
@@ -8589,7 +8589,7 @@
         <v>0015AF</v>
       </c>
     </row>
-    <row r="372" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="372" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B372" s="2">
         <v>348</v>
       </c>
@@ -8602,7 +8602,7 @@
         <v>0015BF</v>
       </c>
     </row>
-    <row r="373" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="373" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B373" s="2">
         <v>349</v>
       </c>
@@ -8615,7 +8615,7 @@
         <v>0015CF</v>
       </c>
     </row>
-    <row r="374" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="374" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B374" s="2">
         <v>350</v>
       </c>
@@ -8628,7 +8628,7 @@
         <v>0015DF</v>
       </c>
     </row>
-    <row r="375" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="375" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B375" s="2">
         <v>351</v>
       </c>
@@ -8641,7 +8641,7 @@
         <v>0015EF</v>
       </c>
     </row>
-    <row r="376" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="376" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B376" s="2">
         <v>352</v>
       </c>
@@ -8654,7 +8654,7 @@
         <v>0015FF</v>
       </c>
     </row>
-    <row r="377" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="377" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B377" s="2">
         <v>353</v>
       </c>
@@ -8667,7 +8667,7 @@
         <v>00160F</v>
       </c>
     </row>
-    <row r="378" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="378" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B378" s="2">
         <v>354</v>
       </c>
@@ -8680,7 +8680,7 @@
         <v>00161F</v>
       </c>
     </row>
-    <row r="379" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="379" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B379" s="2">
         <v>355</v>
       </c>
@@ -8693,7 +8693,7 @@
         <v>00162F</v>
       </c>
     </row>
-    <row r="380" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="380" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B380" s="2">
         <v>356</v>
       </c>
@@ -8706,7 +8706,7 @@
         <v>00163F</v>
       </c>
     </row>
-    <row r="381" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="381" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B381" s="2">
         <v>357</v>
       </c>
@@ -8719,7 +8719,7 @@
         <v>00164F</v>
       </c>
     </row>
-    <row r="382" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="382" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B382" s="2">
         <v>358</v>
       </c>
@@ -8732,7 +8732,7 @@
         <v>00165F</v>
       </c>
     </row>
-    <row r="383" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="383" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B383" s="2">
         <v>359</v>
       </c>
@@ -8745,7 +8745,7 @@
         <v>00166F</v>
       </c>
     </row>
-    <row r="384" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="384" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B384" s="2">
         <v>360</v>
       </c>
@@ -8758,7 +8758,7 @@
         <v>00167F</v>
       </c>
     </row>
-    <row r="385" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="385" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B385" s="2">
         <v>361</v>
       </c>
@@ -8771,7 +8771,7 @@
         <v>00168F</v>
       </c>
     </row>
-    <row r="386" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="386" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B386" s="2">
         <v>362</v>
       </c>
@@ -8784,7 +8784,7 @@
         <v>00169F</v>
       </c>
     </row>
-    <row r="387" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="387" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B387" s="2">
         <v>363</v>
       </c>
@@ -8797,7 +8797,7 @@
         <v>0016AF</v>
       </c>
     </row>
-    <row r="388" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="388" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B388" s="2">
         <v>364</v>
       </c>
@@ -8810,7 +8810,7 @@
         <v>0016BF</v>
       </c>
     </row>
-    <row r="389" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="389" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B389" s="2">
         <v>365</v>
       </c>
@@ -8823,7 +8823,7 @@
         <v>0016CF</v>
       </c>
     </row>
-    <row r="390" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="390" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B390" s="2">
         <v>366</v>
       </c>
@@ -8836,7 +8836,7 @@
         <v>0016DF</v>
       </c>
     </row>
-    <row r="391" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="391" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B391" s="2">
         <v>367</v>
       </c>
@@ -8849,7 +8849,7 @@
         <v>0016EF</v>
       </c>
     </row>
-    <row r="392" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="392" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B392" s="2">
         <v>368</v>
       </c>
@@ -8862,7 +8862,7 @@
         <v>0016FF</v>
       </c>
     </row>
-    <row r="393" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="393" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B393" s="2">
         <v>369</v>
       </c>
@@ -8875,7 +8875,7 @@
         <v>00170F</v>
       </c>
     </row>
-    <row r="394" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="394" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B394" s="2">
         <v>370</v>
       </c>
@@ -8888,7 +8888,7 @@
         <v>00171F</v>
       </c>
     </row>
-    <row r="395" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="395" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B395" s="2">
         <v>371</v>
       </c>
@@ -8901,7 +8901,7 @@
         <v>00172F</v>
       </c>
     </row>
-    <row r="396" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="396" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B396" s="2">
         <v>372</v>
       </c>
@@ -8914,7 +8914,7 @@
         <v>00173F</v>
       </c>
     </row>
-    <row r="397" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="397" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B397" s="2">
         <v>373</v>
       </c>
@@ -8927,7 +8927,7 @@
         <v>00174F</v>
       </c>
     </row>
-    <row r="398" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="398" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B398" s="2">
         <v>374</v>
       </c>
@@ -8940,7 +8940,7 @@
         <v>00175F</v>
       </c>
     </row>
-    <row r="399" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="399" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B399" s="2">
         <v>375</v>
       </c>
@@ -8953,7 +8953,7 @@
         <v>00176F</v>
       </c>
     </row>
-    <row r="400" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="400" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B400" s="2">
         <v>376</v>
       </c>
@@ -8966,7 +8966,7 @@
         <v>00177F</v>
       </c>
     </row>
-    <row r="401" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="401" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B401" s="2">
         <v>377</v>
       </c>
@@ -8979,7 +8979,7 @@
         <v>00178F</v>
       </c>
     </row>
-    <row r="402" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="402" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B402" s="2">
         <v>378</v>
       </c>
@@ -8992,7 +8992,7 @@
         <v>00179F</v>
       </c>
     </row>
-    <row r="403" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="403" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B403" s="2">
         <v>379</v>
       </c>
@@ -9005,7 +9005,7 @@
         <v>0017AF</v>
       </c>
     </row>
-    <row r="404" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="404" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B404" s="2">
         <v>380</v>
       </c>
@@ -9018,7 +9018,7 @@
         <v>0017BF</v>
       </c>
     </row>
-    <row r="405" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="405" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B405" s="2">
         <v>381</v>
       </c>
@@ -9031,7 +9031,7 @@
         <v>0017CF</v>
       </c>
     </row>
-    <row r="406" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="406" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B406" s="2">
         <v>382</v>
       </c>
@@ -9044,7 +9044,7 @@
         <v>0017DF</v>
       </c>
     </row>
-    <row r="407" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="407" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B407" s="2">
         <v>383</v>
       </c>
@@ -9057,7 +9057,7 @@
         <v>0017EF</v>
       </c>
     </row>
-    <row r="408" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="408" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B408" s="2">
         <v>384</v>
       </c>
@@ -9070,7 +9070,7 @@
         <v>0017FF</v>
       </c>
     </row>
-    <row r="409" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="409" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B409" s="2">
         <v>385</v>
       </c>
@@ -9083,7 +9083,7 @@
         <v>00180F</v>
       </c>
     </row>
-    <row r="410" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="410" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B410" s="2">
         <v>386</v>
       </c>
@@ -9096,7 +9096,7 @@
         <v>00181F</v>
       </c>
     </row>
-    <row r="411" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="411" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B411" s="2">
         <v>387</v>
       </c>
@@ -9109,7 +9109,7 @@
         <v>00182F</v>
       </c>
     </row>
-    <row r="412" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="412" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B412" s="2">
         <v>388</v>
       </c>
@@ -9122,7 +9122,7 @@
         <v>00183F</v>
       </c>
     </row>
-    <row r="413" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="413" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B413" s="2">
         <v>389</v>
       </c>
@@ -9135,7 +9135,7 @@
         <v>00184F</v>
       </c>
     </row>
-    <row r="414" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="414" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B414" s="2">
         <v>390</v>
       </c>
@@ -9148,7 +9148,7 @@
         <v>00185F</v>
       </c>
     </row>
-    <row r="415" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="415" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B415" s="2">
         <v>391</v>
       </c>
@@ -9161,7 +9161,7 @@
         <v>00186F</v>
       </c>
     </row>
-    <row r="416" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="416" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B416" s="2">
         <v>392</v>
       </c>
@@ -9174,7 +9174,7 @@
         <v>00187F</v>
       </c>
     </row>
-    <row r="417" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="417" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B417" s="2">
         <v>393</v>
       </c>
@@ -9187,7 +9187,7 @@
         <v>00188F</v>
       </c>
     </row>
-    <row r="418" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="418" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B418" s="2">
         <v>394</v>
       </c>
@@ -9200,7 +9200,7 @@
         <v>00189F</v>
       </c>
     </row>
-    <row r="419" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="419" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B419" s="2">
         <v>395</v>
       </c>
@@ -9213,7 +9213,7 @@
         <v>0018AF</v>
       </c>
     </row>
-    <row r="420" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="420" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B420" s="2">
         <v>396</v>
       </c>
@@ -9226,7 +9226,7 @@
         <v>0018BF</v>
       </c>
     </row>
-    <row r="421" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="421" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B421" s="2">
         <v>397</v>
       </c>
@@ -9239,7 +9239,7 @@
         <v>0018CF</v>
       </c>
     </row>
-    <row r="422" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="422" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B422" s="2">
         <v>398</v>
       </c>
@@ -9252,7 +9252,7 @@
         <v>0018DF</v>
       </c>
     </row>
-    <row r="423" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="423" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B423" s="2">
         <v>399</v>
       </c>
@@ -9265,7 +9265,7 @@
         <v>0018EF</v>
       </c>
     </row>
-    <row r="424" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="424" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B424" s="2">
         <v>400</v>
       </c>
@@ -9278,7 +9278,7 @@
         <v>0018FF</v>
       </c>
     </row>
-    <row r="425" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="425" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B425" s="2">
         <v>401</v>
       </c>
@@ -9291,7 +9291,7 @@
         <v>00190F</v>
       </c>
     </row>
-    <row r="426" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="426" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B426" s="2">
         <v>402</v>
       </c>
@@ -9304,7 +9304,7 @@
         <v>00191F</v>
       </c>
     </row>
-    <row r="427" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="427" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B427" s="2">
         <v>403</v>
       </c>
@@ -9317,7 +9317,7 @@
         <v>00192F</v>
       </c>
     </row>
-    <row r="428" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="428" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B428" s="2">
         <v>404</v>
       </c>
@@ -9330,7 +9330,7 @@
         <v>00193F</v>
       </c>
     </row>
-    <row r="429" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="429" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B429" s="2">
         <v>405</v>
       </c>
@@ -9343,7 +9343,7 @@
         <v>00194F</v>
       </c>
     </row>
-    <row r="430" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="430" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B430" s="2">
         <v>406</v>
       </c>
@@ -9356,7 +9356,7 @@
         <v>00195F</v>
       </c>
     </row>
-    <row r="431" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="431" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B431" s="2">
         <v>407</v>
       </c>
@@ -9369,7 +9369,7 @@
         <v>00196F</v>
       </c>
     </row>
-    <row r="432" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="432" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B432" s="2">
         <v>408</v>
       </c>
@@ -9382,7 +9382,7 @@
         <v>00197F</v>
       </c>
     </row>
-    <row r="433" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="433" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B433" s="2">
         <v>409</v>
       </c>
@@ -9395,7 +9395,7 @@
         <v>00198F</v>
       </c>
     </row>
-    <row r="434" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="434" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B434" s="2">
         <v>410</v>
       </c>
@@ -9408,7 +9408,7 @@
         <v>00199F</v>
       </c>
     </row>
-    <row r="435" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="435" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B435" s="2">
         <v>411</v>
       </c>
@@ -9421,7 +9421,7 @@
         <v>0019AF</v>
       </c>
     </row>
-    <row r="436" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="436" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B436" s="2">
         <v>412</v>
       </c>
@@ -9434,7 +9434,7 @@
         <v>0019BF</v>
       </c>
     </row>
-    <row r="437" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="437" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B437" s="2">
         <v>413</v>
       </c>
@@ -9447,7 +9447,7 @@
         <v>0019CF</v>
       </c>
     </row>
-    <row r="438" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="438" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B438" s="2">
         <v>414</v>
       </c>
@@ -9460,7 +9460,7 @@
         <v>0019DF</v>
       </c>
     </row>
-    <row r="439" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="439" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B439" s="2">
         <v>415</v>
       </c>
@@ -9473,7 +9473,7 @@
         <v>0019EF</v>
       </c>
     </row>
-    <row r="440" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="440" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B440" s="2">
         <v>416</v>
       </c>
@@ -9486,7 +9486,7 @@
         <v>0019FF</v>
       </c>
     </row>
-    <row r="441" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="441" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B441" s="2">
         <v>417</v>
       </c>
@@ -9499,7 +9499,7 @@
         <v>001A0F</v>
       </c>
     </row>
-    <row r="442" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="442" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B442" s="2">
         <v>418</v>
       </c>
@@ -9512,7 +9512,7 @@
         <v>001A1F</v>
       </c>
     </row>
-    <row r="443" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="443" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B443" s="2">
         <v>419</v>
       </c>
@@ -9525,7 +9525,7 @@
         <v>001A2F</v>
       </c>
     </row>
-    <row r="444" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="444" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B444" s="2">
         <v>420</v>
       </c>
@@ -9538,7 +9538,7 @@
         <v>001A3F</v>
       </c>
     </row>
-    <row r="445" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="445" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B445" s="2">
         <v>421</v>
       </c>
@@ -9551,7 +9551,7 @@
         <v>001A4F</v>
       </c>
     </row>
-    <row r="446" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="446" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B446" s="2">
         <v>422</v>
       </c>
@@ -9564,7 +9564,7 @@
         <v>001A5F</v>
       </c>
     </row>
-    <row r="447" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="447" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B447" s="2">
         <v>423</v>
       </c>
@@ -9577,7 +9577,7 @@
         <v>001A6F</v>
       </c>
     </row>
-    <row r="448" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="448" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B448" s="2">
         <v>424</v>
       </c>
@@ -9590,7 +9590,7 @@
         <v>001A7F</v>
       </c>
     </row>
-    <row r="449" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="449" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B449" s="2">
         <v>425</v>
       </c>
@@ -9603,7 +9603,7 @@
         <v>001A8F</v>
       </c>
     </row>
-    <row r="450" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="450" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B450" s="2">
         <v>426</v>
       </c>
@@ -9616,7 +9616,7 @@
         <v>001A9F</v>
       </c>
     </row>
-    <row r="451" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="451" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B451" s="2">
         <v>427</v>
       </c>
@@ -9629,7 +9629,7 @@
         <v>001AAF</v>
       </c>
     </row>
-    <row r="452" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="452" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B452" s="2">
         <v>428</v>
       </c>
@@ -9642,7 +9642,7 @@
         <v>001ABF</v>
       </c>
     </row>
-    <row r="453" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="453" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B453" s="2">
         <v>429</v>
       </c>
@@ -9655,7 +9655,7 @@
         <v>001ACF</v>
       </c>
     </row>
-    <row r="454" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="454" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B454" s="2">
         <v>430</v>
       </c>
@@ -9668,7 +9668,7 @@
         <v>001ADF</v>
       </c>
     </row>
-    <row r="455" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="455" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B455" s="2">
         <v>431</v>
       </c>
@@ -9681,7 +9681,7 @@
         <v>001AEF</v>
       </c>
     </row>
-    <row r="456" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="456" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B456" s="2">
         <v>432</v>
       </c>
@@ -9694,7 +9694,7 @@
         <v>001AFF</v>
       </c>
     </row>
-    <row r="457" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="457" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B457" s="2">
         <v>433</v>
       </c>
@@ -9707,7 +9707,7 @@
         <v>001B0F</v>
       </c>
     </row>
-    <row r="458" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="458" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B458" s="2">
         <v>434</v>
       </c>
@@ -9720,7 +9720,7 @@
         <v>001B1F</v>
       </c>
     </row>
-    <row r="459" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="459" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B459" s="2">
         <v>435</v>
       </c>
@@ -9733,7 +9733,7 @@
         <v>001B2F</v>
       </c>
     </row>
-    <row r="460" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="460" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B460" s="2">
         <v>436</v>
       </c>
@@ -9746,7 +9746,7 @@
         <v>001B3F</v>
       </c>
     </row>
-    <row r="461" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="461" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B461" s="2">
         <v>437</v>
       </c>
@@ -9759,7 +9759,7 @@
         <v>001B4F</v>
       </c>
     </row>
-    <row r="462" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="462" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B462" s="2">
         <v>438</v>
       </c>
@@ -9772,7 +9772,7 @@
         <v>001B5F</v>
       </c>
     </row>
-    <row r="463" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="463" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B463" s="2">
         <v>439</v>
       </c>
@@ -9785,7 +9785,7 @@
         <v>001B6F</v>
       </c>
     </row>
-    <row r="464" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="464" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B464" s="2">
         <v>440</v>
       </c>
@@ -9798,7 +9798,7 @@
         <v>001B7F</v>
       </c>
     </row>
-    <row r="465" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="465" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B465" s="2">
         <v>441</v>
       </c>
@@ -9811,7 +9811,7 @@
         <v>001B8F</v>
       </c>
     </row>
-    <row r="466" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="466" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B466" s="2">
         <v>442</v>
       </c>
@@ -9824,7 +9824,7 @@
         <v>001B9F</v>
       </c>
     </row>
-    <row r="467" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="467" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B467" s="2">
         <v>443</v>
       </c>
@@ -9837,7 +9837,7 @@
         <v>001BAF</v>
       </c>
     </row>
-    <row r="468" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="468" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B468" s="2">
         <v>444</v>
       </c>
@@ -9850,7 +9850,7 @@
         <v>001BBF</v>
       </c>
     </row>
-    <row r="469" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="469" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B469" s="2">
         <v>445</v>
       </c>
@@ -9863,7 +9863,7 @@
         <v>001BCF</v>
       </c>
     </row>
-    <row r="470" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="470" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B470" s="2">
         <v>446</v>
       </c>
@@ -9876,7 +9876,7 @@
         <v>001BDF</v>
       </c>
     </row>
-    <row r="471" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="471" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B471" s="2">
         <v>447</v>
       </c>
@@ -9889,7 +9889,7 @@
         <v>001BEF</v>
       </c>
     </row>
-    <row r="472" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="472" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B472" s="2">
         <v>448</v>
       </c>
@@ -9902,7 +9902,7 @@
         <v>001BFF</v>
       </c>
     </row>
-    <row r="473" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="473" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B473" s="2">
         <v>449</v>
       </c>
@@ -9915,7 +9915,7 @@
         <v>001C0F</v>
       </c>
     </row>
-    <row r="474" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="474" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B474" s="2">
         <v>450</v>
       </c>
@@ -9928,7 +9928,7 @@
         <v>001C1F</v>
       </c>
     </row>
-    <row r="475" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="475" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B475" s="2">
         <v>451</v>
       </c>
@@ -9941,7 +9941,7 @@
         <v>001C2F</v>
       </c>
     </row>
-    <row r="476" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="476" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B476" s="2">
         <v>452</v>
       </c>
@@ -9954,7 +9954,7 @@
         <v>001C3F</v>
       </c>
     </row>
-    <row r="477" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="477" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B477" s="2">
         <v>453</v>
       </c>
@@ -9967,7 +9967,7 @@
         <v>001C4F</v>
       </c>
     </row>
-    <row r="478" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="478" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B478" s="2">
         <v>454</v>
       </c>
@@ -9980,7 +9980,7 @@
         <v>001C5F</v>
       </c>
     </row>
-    <row r="479" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="479" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B479" s="2">
         <v>455</v>
       </c>
@@ -9993,7 +9993,7 @@
         <v>001C6F</v>
       </c>
     </row>
-    <row r="480" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="480" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B480" s="2">
         <v>456</v>
       </c>
@@ -10006,7 +10006,7 @@
         <v>001C7F</v>
       </c>
     </row>
-    <row r="481" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="481" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B481" s="2">
         <v>457</v>
       </c>
@@ -10019,7 +10019,7 @@
         <v>001C8F</v>
       </c>
     </row>
-    <row r="482" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="482" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B482" s="2">
         <v>458</v>
       </c>
@@ -10032,7 +10032,7 @@
         <v>001C9F</v>
       </c>
     </row>
-    <row r="483" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="483" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B483" s="2">
         <v>459</v>
       </c>
@@ -10045,7 +10045,7 @@
         <v>001CAF</v>
       </c>
     </row>
-    <row r="484" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="484" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B484" s="2">
         <v>460</v>
       </c>
@@ -10058,7 +10058,7 @@
         <v>001CBF</v>
       </c>
     </row>
-    <row r="485" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="485" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B485" s="2">
         <v>461</v>
       </c>
@@ -10071,7 +10071,7 @@
         <v>001CCF</v>
       </c>
     </row>
-    <row r="486" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="486" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B486" s="2">
         <v>462</v>
       </c>
@@ -10084,7 +10084,7 @@
         <v>001CDF</v>
       </c>
     </row>
-    <row r="487" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="487" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B487" s="2">
         <v>463</v>
       </c>
@@ -10097,7 +10097,7 @@
         <v>001CEF</v>
       </c>
     </row>
-    <row r="488" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="488" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B488" s="2">
         <v>464</v>
       </c>
@@ -10110,7 +10110,7 @@
         <v>001CFF</v>
       </c>
     </row>
-    <row r="489" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="489" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B489" s="2">
         <v>465</v>
       </c>
@@ -10123,7 +10123,7 @@
         <v>001D0F</v>
       </c>
     </row>
-    <row r="490" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="490" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B490" s="2">
         <v>466</v>
       </c>
@@ -10136,7 +10136,7 @@
         <v>001D1F</v>
       </c>
     </row>
-    <row r="491" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="491" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B491" s="2">
         <v>467</v>
       </c>
@@ -10149,7 +10149,7 @@
         <v>001D2F</v>
       </c>
     </row>
-    <row r="492" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="492" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B492" s="2">
         <v>468</v>
       </c>
@@ -10162,7 +10162,7 @@
         <v>001D3F</v>
       </c>
     </row>
-    <row r="493" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="493" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B493" s="2">
         <v>469</v>
       </c>
@@ -10175,7 +10175,7 @@
         <v>001D4F</v>
       </c>
     </row>
-    <row r="494" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="494" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B494" s="2">
         <v>470</v>
       </c>
@@ -10188,7 +10188,7 @@
         <v>001D5F</v>
       </c>
     </row>
-    <row r="495" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="495" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B495" s="2">
         <v>471</v>
       </c>
@@ -10201,7 +10201,7 @@
         <v>001D6F</v>
       </c>
     </row>
-    <row r="496" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="496" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B496" s="2">
         <v>472</v>
       </c>
@@ -10214,7 +10214,7 @@
         <v>001D7F</v>
       </c>
     </row>
-    <row r="497" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="497" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B497" s="2">
         <v>473</v>
       </c>
@@ -10227,7 +10227,7 @@
         <v>001D8F</v>
       </c>
     </row>
-    <row r="498" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="498" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B498" s="2">
         <v>474</v>
       </c>
@@ -10240,7 +10240,7 @@
         <v>001D9F</v>
       </c>
     </row>
-    <row r="499" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="499" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B499" s="2">
         <v>475</v>
       </c>
@@ -10253,7 +10253,7 @@
         <v>001DAF</v>
       </c>
     </row>
-    <row r="500" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="500" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B500" s="2">
         <v>476</v>
       </c>
@@ -10266,7 +10266,7 @@
         <v>001DBF</v>
       </c>
     </row>
-    <row r="501" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="501" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B501" s="2">
         <v>477</v>
       </c>
@@ -10279,7 +10279,7 @@
         <v>001DCF</v>
       </c>
     </row>
-    <row r="502" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="502" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B502" s="2">
         <v>478</v>
       </c>
@@ -10292,7 +10292,7 @@
         <v>001DDF</v>
       </c>
     </row>
-    <row r="503" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="503" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B503" s="2">
         <v>479</v>
       </c>
@@ -10305,7 +10305,7 @@
         <v>001DEF</v>
       </c>
     </row>
-    <row r="504" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="504" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B504" s="2">
         <v>480</v>
       </c>
@@ -10318,7 +10318,7 @@
         <v>001DFF</v>
       </c>
     </row>
-    <row r="505" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="505" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B505" s="2">
         <v>481</v>
       </c>
@@ -10331,7 +10331,7 @@
         <v>001E0F</v>
       </c>
     </row>
-    <row r="506" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="506" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B506" s="2">
         <v>482</v>
       </c>
@@ -10344,7 +10344,7 @@
         <v>001E1F</v>
       </c>
     </row>
-    <row r="507" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="507" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B507" s="2">
         <v>483</v>
       </c>
@@ -10357,7 +10357,7 @@
         <v>001E2F</v>
       </c>
     </row>
-    <row r="508" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="508" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B508" s="2">
         <v>484</v>
       </c>
@@ -10370,7 +10370,7 @@
         <v>001E3F</v>
       </c>
     </row>
-    <row r="509" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="509" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B509" s="2">
         <v>485</v>
       </c>
@@ -10383,7 +10383,7 @@
         <v>001E4F</v>
       </c>
     </row>
-    <row r="510" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="510" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B510" s="2">
         <v>486</v>
       </c>
@@ -10396,7 +10396,7 @@
         <v>001E5F</v>
       </c>
     </row>
-    <row r="511" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="511" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B511" s="2">
         <v>487</v>
       </c>
@@ -10409,7 +10409,7 @@
         <v>001E6F</v>
       </c>
     </row>
-    <row r="512" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="512" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B512" s="2">
         <v>488</v>
       </c>
@@ -10422,7 +10422,7 @@
         <v>001E7F</v>
       </c>
     </row>
-    <row r="513" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="513" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B513" s="2">
         <v>489</v>
       </c>
@@ -10435,7 +10435,7 @@
         <v>001E8F</v>
       </c>
     </row>
-    <row r="514" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="514" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B514" s="2">
         <v>490</v>
       </c>
@@ -10448,7 +10448,7 @@
         <v>001E9F</v>
       </c>
     </row>
-    <row r="515" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="515" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B515" s="2">
         <v>491</v>
       </c>
@@ -10461,7 +10461,7 @@
         <v>001EAF</v>
       </c>
     </row>
-    <row r="516" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="516" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B516" s="2">
         <v>492</v>
       </c>
@@ -10474,7 +10474,7 @@
         <v>001EBF</v>
       </c>
     </row>
-    <row r="517" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="517" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B517" s="2">
         <v>493</v>
       </c>
@@ -10487,7 +10487,7 @@
         <v>001ECF</v>
       </c>
     </row>
-    <row r="518" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="518" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B518" s="2">
         <v>494</v>
       </c>
@@ -10500,7 +10500,7 @@
         <v>001EDF</v>
       </c>
     </row>
-    <row r="519" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="519" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B519" s="2">
         <v>495</v>
       </c>
@@ -10513,7 +10513,7 @@
         <v>001EEF</v>
       </c>
     </row>
-    <row r="520" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="520" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B520" s="2">
         <v>496</v>
       </c>
@@ -10526,7 +10526,7 @@
         <v>001EFF</v>
       </c>
     </row>
-    <row r="521" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="521" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B521" s="2">
         <v>497</v>
       </c>
@@ -10539,7 +10539,7 @@
         <v>001F0F</v>
       </c>
     </row>
-    <row r="522" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="522" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B522" s="2">
         <v>498</v>
       </c>
@@ -10552,7 +10552,7 @@
         <v>001F1F</v>
       </c>
     </row>
-    <row r="523" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="523" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B523" s="2">
         <v>499</v>
       </c>
@@ -10565,7 +10565,7 @@
         <v>001F2F</v>
       </c>
     </row>
-    <row r="524" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="524" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B524" s="2">
         <v>500</v>
       </c>
@@ -10578,7 +10578,7 @@
         <v>001F3F</v>
       </c>
     </row>
-    <row r="525" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="525" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B525" s="2">
         <v>501</v>
       </c>
@@ -10591,7 +10591,7 @@
         <v>001F4F</v>
       </c>
     </row>
-    <row r="526" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="526" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B526" s="2">
         <v>502</v>
       </c>
@@ -10604,7 +10604,7 @@
         <v>001F5F</v>
       </c>
     </row>
-    <row r="527" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="527" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B527" s="2">
         <v>503</v>
       </c>
@@ -10617,7 +10617,7 @@
         <v>001F6F</v>
       </c>
     </row>
-    <row r="528" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="528" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B528" s="2">
         <v>504</v>
       </c>
@@ -10630,7 +10630,7 @@
         <v>001F7F</v>
       </c>
     </row>
-    <row r="529" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="529" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B529" s="2">
         <v>505</v>
       </c>
@@ -10643,7 +10643,7 @@
         <v>001F8F</v>
       </c>
     </row>
-    <row r="530" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="530" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B530" s="2">
         <v>506</v>
       </c>
@@ -10656,7 +10656,7 @@
         <v>001F9F</v>
       </c>
     </row>
-    <row r="531" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="531" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B531" s="2">
         <v>507</v>
       </c>
@@ -10669,7 +10669,7 @@
         <v>001FAF</v>
       </c>
     </row>
-    <row r="532" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="532" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B532" s="2">
         <v>508</v>
       </c>
@@ -10682,7 +10682,7 @@
         <v>001FBF</v>
       </c>
     </row>
-    <row r="533" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="533" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B533" s="2">
         <v>509</v>
       </c>
@@ -10695,7 +10695,7 @@
         <v>001FCF</v>
       </c>
     </row>
-    <row r="534" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="534" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B534" s="2">
         <v>510</v>
       </c>
@@ -10708,7 +10708,7 @@
         <v>001FDF</v>
       </c>
     </row>
-    <row r="535" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="535" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B535" s="2">
         <v>511</v>
       </c>
@@ -10721,7 +10721,7 @@
         <v>001FEF</v>
       </c>
     </row>
-    <row r="536" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="536" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B536" s="2">
         <v>512</v>
       </c>
@@ -10734,7 +10734,7 @@
         <v>001FFF</v>
       </c>
     </row>
-    <row r="537" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="537" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B537" s="2">
         <v>513</v>
       </c>
@@ -10747,7 +10747,7 @@
         <v>00200F</v>
       </c>
     </row>
-    <row r="538" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="538" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B538" s="2">
         <v>514</v>
       </c>
@@ -10760,7 +10760,7 @@
         <v>00201F</v>
       </c>
     </row>
-    <row r="539" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="539" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B539" s="2">
         <v>515</v>
       </c>
@@ -10773,7 +10773,7 @@
         <v>00202F</v>
       </c>
     </row>
-    <row r="540" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="540" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B540" s="2">
         <v>516</v>
       </c>
@@ -10786,7 +10786,7 @@
         <v>00203F</v>
       </c>
     </row>
-    <row r="541" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="541" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B541" s="2">
         <v>517</v>
       </c>
@@ -10799,7 +10799,7 @@
         <v>00204F</v>
       </c>
     </row>
-    <row r="542" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="542" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B542" s="2">
         <v>518</v>
       </c>
@@ -10812,7 +10812,7 @@
         <v>00205F</v>
       </c>
     </row>
-    <row r="543" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="543" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B543" s="2">
         <v>519</v>
       </c>
@@ -10825,7 +10825,7 @@
         <v>00206F</v>
       </c>
     </row>
-    <row r="544" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="544" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B544" s="2">
         <v>520</v>
       </c>
@@ -10838,7 +10838,7 @@
         <v>00207F</v>
       </c>
     </row>
-    <row r="545" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="545" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B545" s="2">
         <v>521</v>
       </c>
@@ -10851,7 +10851,7 @@
         <v>00208F</v>
       </c>
     </row>
-    <row r="546" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="546" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B546" s="2">
         <v>522</v>
       </c>
@@ -10864,7 +10864,7 @@
         <v>00209F</v>
       </c>
     </row>
-    <row r="547" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="547" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B547" s="2">
         <v>523</v>
       </c>
@@ -10877,7 +10877,7 @@
         <v>0020AF</v>
       </c>
     </row>
-    <row r="548" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="548" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B548" s="2">
         <v>524</v>
       </c>
@@ -10890,7 +10890,7 @@
         <v>0020BF</v>
       </c>
     </row>
-    <row r="549" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="549" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B549" s="2">
         <v>525</v>
       </c>
@@ -10903,7 +10903,7 @@
         <v>0020CF</v>
       </c>
     </row>
-    <row r="550" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="550" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B550" s="2">
         <v>526</v>
       </c>
@@ -10916,7 +10916,7 @@
         <v>0020DF</v>
       </c>
     </row>
-    <row r="551" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="551" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B551" s="2">
         <v>527</v>
       </c>
@@ -10929,7 +10929,7 @@
         <v>0020EF</v>
       </c>
     </row>
-    <row r="552" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="552" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B552" s="2">
         <v>528</v>
       </c>
@@ -10942,7 +10942,7 @@
         <v>0020FF</v>
       </c>
     </row>
-    <row r="553" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="553" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B553" s="2">
         <v>529</v>
       </c>
@@ -10955,7 +10955,7 @@
         <v>00210F</v>
       </c>
     </row>
-    <row r="554" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="554" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B554" s="2">
         <v>530</v>
       </c>
@@ -10968,7 +10968,7 @@
         <v>00211F</v>
       </c>
     </row>
-    <row r="555" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="555" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B555" s="2">
         <v>531</v>
       </c>
@@ -10981,7 +10981,7 @@
         <v>00212F</v>
       </c>
     </row>
-    <row r="556" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="556" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B556" s="2">
         <v>532</v>
       </c>
@@ -10994,7 +10994,7 @@
         <v>00213F</v>
       </c>
     </row>
-    <row r="557" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="557" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B557" s="2">
         <v>533</v>
       </c>
@@ -11007,7 +11007,7 @@
         <v>00214F</v>
       </c>
     </row>
-    <row r="558" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="558" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B558" s="2">
         <v>534</v>
       </c>
@@ -11020,7 +11020,7 @@
         <v>00215F</v>
       </c>
     </row>
-    <row r="559" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="559" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B559" s="2">
         <v>535</v>
       </c>
@@ -11033,7 +11033,7 @@
         <v>00216F</v>
       </c>
     </row>
-    <row r="560" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="560" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B560" s="2">
         <v>536</v>
       </c>
@@ -11046,7 +11046,7 @@
         <v>00217F</v>
       </c>
     </row>
-    <row r="561" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="561" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B561" s="2">
         <v>537</v>
       </c>
@@ -11059,7 +11059,7 @@
         <v>00218F</v>
       </c>
     </row>
-    <row r="562" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="562" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B562" s="2">
         <v>538</v>
       </c>
@@ -11072,7 +11072,7 @@
         <v>00219F</v>
       </c>
     </row>
-    <row r="563" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="563" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B563" s="2">
         <v>539</v>
       </c>
@@ -11085,7 +11085,7 @@
         <v>0021AF</v>
       </c>
     </row>
-    <row r="564" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="564" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B564" s="2">
         <v>540</v>
       </c>
@@ -11098,7 +11098,7 @@
         <v>0021BF</v>
       </c>
     </row>
-    <row r="565" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="565" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B565" s="2">
         <v>541</v>
       </c>
@@ -11111,7 +11111,7 @@
         <v>0021CF</v>
       </c>
     </row>
-    <row r="566" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="566" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B566" s="2">
         <v>542</v>
       </c>
@@ -11124,7 +11124,7 @@
         <v>0021DF</v>
       </c>
     </row>
-    <row r="567" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="567" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B567" s="2">
         <v>543</v>
       </c>
@@ -11137,7 +11137,7 @@
         <v>0021EF</v>
       </c>
     </row>
-    <row r="568" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="568" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B568" s="2">
         <v>544</v>
       </c>
@@ -11150,7 +11150,7 @@
         <v>0021FF</v>
       </c>
     </row>
-    <row r="569" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="569" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B569" s="2">
         <v>545</v>
       </c>
@@ -11163,7 +11163,7 @@
         <v>00220F</v>
       </c>
     </row>
-    <row r="570" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="570" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B570" s="2">
         <v>546</v>
       </c>
@@ -11176,7 +11176,7 @@
         <v>00221F</v>
       </c>
     </row>
-    <row r="571" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="571" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B571" s="2">
         <v>547</v>
       </c>
@@ -11189,7 +11189,7 @@
         <v>00222F</v>
       </c>
     </row>
-    <row r="572" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="572" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B572" s="2">
         <v>548</v>
       </c>
@@ -11202,7 +11202,7 @@
         <v>00223F</v>
       </c>
     </row>
-    <row r="573" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="573" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B573" s="2">
         <v>549</v>
       </c>
@@ -11215,7 +11215,7 @@
         <v>00224F</v>
       </c>
     </row>
-    <row r="574" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="574" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B574" s="2">
         <v>550</v>
       </c>
@@ -11228,7 +11228,7 @@
         <v>00225F</v>
       </c>
     </row>
-    <row r="575" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="575" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B575" s="2">
         <v>551</v>
       </c>
@@ -11241,7 +11241,7 @@
         <v>00226F</v>
       </c>
     </row>
-    <row r="576" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="576" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B576" s="2">
         <v>552</v>
       </c>
@@ -11254,7 +11254,7 @@
         <v>00227F</v>
       </c>
     </row>
-    <row r="577" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="577" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B577" s="2">
         <v>553</v>
       </c>
@@ -11267,7 +11267,7 @@
         <v>00228F</v>
       </c>
     </row>
-    <row r="578" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="578" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B578" s="2">
         <v>554</v>
       </c>
@@ -11280,7 +11280,7 @@
         <v>00229F</v>
       </c>
     </row>
-    <row r="579" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="579" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B579" s="2">
         <v>555</v>
       </c>
@@ -11293,7 +11293,7 @@
         <v>0022AF</v>
       </c>
     </row>
-    <row r="580" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="580" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B580" s="2">
         <v>556</v>
       </c>
@@ -11306,7 +11306,7 @@
         <v>0022BF</v>
       </c>
     </row>
-    <row r="581" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="581" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B581" s="2">
         <v>557</v>
       </c>
@@ -11319,7 +11319,7 @@
         <v>0022CF</v>
       </c>
     </row>
-    <row r="582" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="582" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B582" s="2">
         <v>558</v>
       </c>
@@ -11332,7 +11332,7 @@
         <v>0022DF</v>
       </c>
     </row>
-    <row r="583" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="583" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B583" s="2">
         <v>559</v>
       </c>
@@ -11345,7 +11345,7 @@
         <v>0022EF</v>
       </c>
     </row>
-    <row r="584" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="584" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B584" s="2">
         <v>560</v>
       </c>
@@ -11358,7 +11358,7 @@
         <v>0022FF</v>
       </c>
     </row>
-    <row r="585" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="585" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B585" s="2">
         <v>561</v>
       </c>
@@ -11371,7 +11371,7 @@
         <v>00230F</v>
       </c>
     </row>
-    <row r="586" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="586" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B586" s="2">
         <v>562</v>
       </c>
@@ -11384,7 +11384,7 @@
         <v>00231F</v>
       </c>
     </row>
-    <row r="587" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="587" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B587" s="2">
         <v>563</v>
       </c>
@@ -11397,7 +11397,7 @@
         <v>00232F</v>
       </c>
     </row>
-    <row r="588" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="588" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B588" s="2">
         <v>564</v>
       </c>
@@ -11410,7 +11410,7 @@
         <v>00233F</v>
       </c>
     </row>
-    <row r="589" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="589" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B589" s="2">
         <v>565</v>
       </c>
@@ -11423,7 +11423,7 @@
         <v>00234F</v>
       </c>
     </row>
-    <row r="590" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="590" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B590" s="2">
         <v>566</v>
       </c>
@@ -11436,7 +11436,7 @@
         <v>00235F</v>
       </c>
     </row>
-    <row r="591" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="591" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B591" s="2">
         <v>567</v>
       </c>
@@ -11449,7 +11449,7 @@
         <v>00236F</v>
       </c>
     </row>
-    <row r="592" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="592" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B592" s="2">
         <v>568</v>
       </c>
@@ -11462,7 +11462,7 @@
         <v>00237F</v>
       </c>
     </row>
-    <row r="593" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="593" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B593" s="2">
         <v>569</v>
       </c>
@@ -11475,7 +11475,7 @@
         <v>00238F</v>
       </c>
     </row>
-    <row r="594" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="594" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B594" s="2">
         <v>570</v>
       </c>
@@ -11488,7 +11488,7 @@
         <v>00239F</v>
       </c>
     </row>
-    <row r="595" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="595" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B595" s="2">
         <v>571</v>
       </c>
@@ -11501,7 +11501,7 @@
         <v>0023AF</v>
       </c>
     </row>
-    <row r="596" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="596" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B596" s="2">
         <v>572</v>
       </c>
@@ -11514,7 +11514,7 @@
         <v>0023BF</v>
       </c>
     </row>
-    <row r="597" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="597" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B597" s="2">
         <v>573</v>
       </c>
@@ -11527,7 +11527,7 @@
         <v>0023CF</v>
       </c>
     </row>
-    <row r="598" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="598" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B598" s="2">
         <v>574</v>
       </c>
@@ -11540,7 +11540,7 @@
         <v>0023DF</v>
       </c>
     </row>
-    <row r="599" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="599" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B599" s="2">
         <v>575</v>
       </c>
@@ -11553,7 +11553,7 @@
         <v>0023EF</v>
       </c>
     </row>
-    <row r="600" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="600" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B600" s="2">
         <v>576</v>
       </c>
@@ -11566,7 +11566,7 @@
         <v>0023FF</v>
       </c>
     </row>
-    <row r="601" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="601" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B601" s="2">
         <v>577</v>
       </c>
@@ -11579,7 +11579,7 @@
         <v>00240F</v>
       </c>
     </row>
-    <row r="602" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="602" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B602" s="2">
         <v>578</v>
       </c>
@@ -11592,7 +11592,7 @@
         <v>00241F</v>
       </c>
     </row>
-    <row r="603" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="603" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B603" s="2">
         <v>579</v>
       </c>
@@ -11605,7 +11605,7 @@
         <v>00242F</v>
       </c>
     </row>
-    <row r="604" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="604" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B604" s="2">
         <v>580</v>
       </c>
@@ -11618,7 +11618,7 @@
         <v>00243F</v>
       </c>
     </row>
-    <row r="605" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="605" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B605" s="2">
         <v>581</v>
       </c>
@@ -11631,7 +11631,7 @@
         <v>00244F</v>
       </c>
     </row>
-    <row r="606" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="606" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B606" s="2">
         <v>582</v>
       </c>
@@ -11644,7 +11644,7 @@
         <v>00245F</v>
       </c>
     </row>
-    <row r="607" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="607" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B607" s="2">
         <v>583</v>
       </c>
@@ -11657,7 +11657,7 @@
         <v>00246F</v>
       </c>
     </row>
-    <row r="608" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="608" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B608" s="2">
         <v>584</v>
       </c>
@@ -11670,7 +11670,7 @@
         <v>00247F</v>
       </c>
     </row>
-    <row r="609" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="609" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B609" s="2">
         <v>585</v>
       </c>
@@ -11683,7 +11683,7 @@
         <v>00248F</v>
       </c>
     </row>
-    <row r="610" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="610" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B610" s="2">
         <v>586</v>
       </c>
@@ -11696,7 +11696,7 @@
         <v>00249F</v>
       </c>
     </row>
-    <row r="611" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="611" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B611" s="2">
         <v>587</v>
       </c>
@@ -11709,7 +11709,7 @@
         <v>0024AF</v>
       </c>
     </row>
-    <row r="612" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="612" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B612" s="2">
         <v>588</v>
       </c>
@@ -11722,7 +11722,7 @@
         <v>0024BF</v>
       </c>
     </row>
-    <row r="613" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="613" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B613" s="2">
         <v>589</v>
       </c>
@@ -11735,7 +11735,7 @@
         <v>0024CF</v>
       </c>
     </row>
-    <row r="614" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="614" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B614" s="2">
         <v>590</v>
       </c>
@@ -11748,7 +11748,7 @@
         <v>0024DF</v>
       </c>
     </row>
-    <row r="615" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="615" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B615" s="2">
         <v>591</v>
       </c>
@@ -11761,7 +11761,7 @@
         <v>0024EF</v>
       </c>
     </row>
-    <row r="616" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="616" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B616" s="2">
         <v>592</v>
       </c>
@@ -11774,7 +11774,7 @@
         <v>0024FF</v>
       </c>
     </row>
-    <row r="617" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="617" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B617" s="2">
         <v>593</v>
       </c>
@@ -11787,7 +11787,7 @@
         <v>00250F</v>
       </c>
     </row>
-    <row r="618" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="618" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B618" s="2">
         <v>594</v>
       </c>
@@ -11800,7 +11800,7 @@
         <v>00251F</v>
       </c>
     </row>
-    <row r="619" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="619" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B619" s="2">
         <v>595</v>
       </c>
@@ -11813,7 +11813,7 @@
         <v>00252F</v>
       </c>
     </row>
-    <row r="620" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="620" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B620" s="2">
         <v>596</v>
       </c>
@@ -11826,7 +11826,7 @@
         <v>00253F</v>
       </c>
     </row>
-    <row r="621" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="621" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B621" s="2">
         <v>597</v>
       </c>
@@ -11839,7 +11839,7 @@
         <v>00254F</v>
       </c>
     </row>
-    <row r="622" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="622" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B622" s="2">
         <v>598</v>
       </c>
@@ -11852,7 +11852,7 @@
         <v>00255F</v>
       </c>
     </row>
-    <row r="623" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="623" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B623" s="2">
         <v>599</v>
       </c>
@@ -11865,7 +11865,7 @@
         <v>00256F</v>
       </c>
     </row>
-    <row r="624" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="624" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B624" s="2">
         <v>600</v>
       </c>
@@ -11878,7 +11878,7 @@
         <v>00257F</v>
       </c>
     </row>
-    <row r="625" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="625" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B625" s="2">
         <v>601</v>
       </c>
@@ -11891,7 +11891,7 @@
         <v>00258F</v>
       </c>
     </row>
-    <row r="626" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="626" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B626" s="2">
         <v>602</v>
       </c>
@@ -11904,7 +11904,7 @@
         <v>00259F</v>
       </c>
     </row>
-    <row r="627" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="627" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B627" s="2">
         <v>603</v>
       </c>
@@ -11917,7 +11917,7 @@
         <v>0025AF</v>
       </c>
     </row>
-    <row r="628" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="628" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B628" s="2">
         <v>604</v>
       </c>
@@ -11930,7 +11930,7 @@
         <v>0025BF</v>
       </c>
     </row>
-    <row r="629" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="629" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B629" s="2">
         <v>605</v>
       </c>
@@ -11943,7 +11943,7 @@
         <v>0025CF</v>
       </c>
     </row>
-    <row r="630" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="630" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B630" s="2">
         <v>606</v>
       </c>
@@ -11956,7 +11956,7 @@
         <v>0025DF</v>
       </c>
     </row>
-    <row r="631" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="631" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B631" s="2">
         <v>607</v>
       </c>
@@ -11969,7 +11969,7 @@
         <v>0025EF</v>
       </c>
     </row>
-    <row r="632" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="632" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B632" s="2">
         <v>608</v>
       </c>
@@ -11982,7 +11982,7 @@
         <v>0025FF</v>
       </c>
     </row>
-    <row r="633" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="633" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B633" s="2">
         <v>609</v>
       </c>
@@ -11995,7 +11995,7 @@
         <v>00260F</v>
       </c>
     </row>
-    <row r="634" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="634" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B634" s="2">
         <v>610</v>
       </c>
@@ -12008,7 +12008,7 @@
         <v>00261F</v>
       </c>
     </row>
-    <row r="635" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="635" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B635" s="2">
         <v>611</v>
       </c>
@@ -12021,7 +12021,7 @@
         <v>00262F</v>
       </c>
     </row>
-    <row r="636" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="636" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B636" s="2">
         <v>612</v>
       </c>
@@ -12034,7 +12034,7 @@
         <v>00263F</v>
       </c>
     </row>
-    <row r="637" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="637" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B637" s="2">
         <v>613</v>
       </c>
@@ -12047,7 +12047,7 @@
         <v>00264F</v>
       </c>
     </row>
-    <row r="638" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="638" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B638" s="2">
         <v>614</v>
       </c>
@@ -12060,7 +12060,7 @@
         <v>00265F</v>
       </c>
     </row>
-    <row r="639" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="639" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B639" s="2">
         <v>615</v>
       </c>
@@ -12073,7 +12073,7 @@
         <v>00266F</v>
       </c>
     </row>
-    <row r="640" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="640" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B640" s="2">
         <v>616</v>
       </c>
@@ -12086,7 +12086,7 @@
         <v>00267F</v>
       </c>
     </row>
-    <row r="641" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="641" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B641" s="2">
         <v>617</v>
       </c>
@@ -12099,7 +12099,7 @@
         <v>00268F</v>
       </c>
     </row>
-    <row r="642" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="642" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B642" s="2">
         <v>618</v>
       </c>
@@ -12112,7 +12112,7 @@
         <v>00269F</v>
       </c>
     </row>
-    <row r="643" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="643" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B643" s="2">
         <v>619</v>
       </c>
@@ -12125,7 +12125,7 @@
         <v>0026AF</v>
       </c>
     </row>
-    <row r="644" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="644" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B644" s="2">
         <v>620</v>
       </c>
@@ -12138,7 +12138,7 @@
         <v>0026BF</v>
       </c>
     </row>
-    <row r="645" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="645" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B645" s="2">
         <v>621</v>
       </c>
@@ -12151,7 +12151,7 @@
         <v>0026CF</v>
       </c>
     </row>
-    <row r="646" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="646" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B646" s="2">
         <v>622</v>
       </c>
@@ -12164,7 +12164,7 @@
         <v>0026DF</v>
       </c>
     </row>
-    <row r="647" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="647" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B647" s="2">
         <v>623</v>
       </c>
@@ -12177,7 +12177,7 @@
         <v>0026EF</v>
       </c>
     </row>
-    <row r="648" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="648" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B648" s="2">
         <v>624</v>
       </c>
@@ -12190,7 +12190,7 @@
         <v>0026FF</v>
       </c>
     </row>
-    <row r="649" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="649" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B649" s="2">
         <v>625</v>
       </c>
@@ -12203,7 +12203,7 @@
         <v>00270F</v>
       </c>
     </row>
-    <row r="650" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="650" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B650" s="2">
         <v>626</v>
       </c>
@@ -12216,7 +12216,7 @@
         <v>00271F</v>
       </c>
     </row>
-    <row r="651" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="651" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B651" s="2">
         <v>627</v>
       </c>
@@ -12229,7 +12229,7 @@
         <v>00272F</v>
       </c>
     </row>
-    <row r="652" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="652" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B652" s="2">
         <v>628</v>
       </c>
@@ -12242,7 +12242,7 @@
         <v>00273F</v>
       </c>
     </row>
-    <row r="653" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="653" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B653" s="2">
         <v>629</v>
       </c>
@@ -12255,7 +12255,7 @@
         <v>00274F</v>
       </c>
     </row>
-    <row r="654" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="654" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B654" s="2">
         <v>630</v>
       </c>
@@ -12268,7 +12268,7 @@
         <v>00275F</v>
       </c>
     </row>
-    <row r="655" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="655" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B655" s="2">
         <v>631</v>
       </c>
@@ -12281,7 +12281,7 @@
         <v>00276F</v>
       </c>
     </row>
-    <row r="656" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="656" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B656" s="2">
         <v>632</v>
       </c>
@@ -12294,7 +12294,7 @@
         <v>00277F</v>
       </c>
     </row>
-    <row r="657" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="657" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B657" s="2">
         <v>633</v>
       </c>
@@ -12307,7 +12307,7 @@
         <v>00278F</v>
       </c>
     </row>
-    <row r="658" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="658" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B658" s="2">
         <v>634</v>
       </c>
@@ -12320,7 +12320,7 @@
         <v>00279F</v>
       </c>
     </row>
-    <row r="659" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="659" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B659" s="2">
         <v>635</v>
       </c>
@@ -12333,7 +12333,7 @@
         <v>0027AF</v>
       </c>
     </row>
-    <row r="660" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="660" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B660" s="2">
         <v>636</v>
       </c>
@@ -12346,7 +12346,7 @@
         <v>0027BF</v>
       </c>
     </row>
-    <row r="661" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="661" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B661" s="2">
         <v>637</v>
       </c>
@@ -12359,7 +12359,7 @@
         <v>0027CF</v>
       </c>
     </row>
-    <row r="662" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="662" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B662" s="2">
         <v>638</v>
       </c>
@@ -12372,7 +12372,7 @@
         <v>0027DF</v>
       </c>
     </row>
-    <row r="663" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="663" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B663" s="2">
         <v>639</v>
       </c>
@@ -12385,7 +12385,7 @@
         <v>0027EF</v>
       </c>
     </row>
-    <row r="664" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="664" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B664" s="2">
         <v>640</v>
       </c>
@@ -12398,7 +12398,7 @@
         <v>0027FF</v>
       </c>
     </row>
-    <row r="665" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="665" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B665" s="2">
         <v>641</v>
       </c>
@@ -12411,7 +12411,7 @@
         <v>00280F</v>
       </c>
     </row>
-    <row r="666" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="666" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B666" s="2">
         <v>642</v>
       </c>
@@ -12424,7 +12424,7 @@
         <v>00281F</v>
       </c>
     </row>
-    <row r="667" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="667" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B667" s="2">
         <v>643</v>
       </c>
@@ -12437,7 +12437,7 @@
         <v>00282F</v>
       </c>
     </row>
-    <row r="668" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="668" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B668" s="2">
         <v>644</v>
       </c>
@@ -12450,7 +12450,7 @@
         <v>00283F</v>
       </c>
     </row>
-    <row r="669" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="669" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B669" s="2">
         <v>645</v>
       </c>
@@ -12463,7 +12463,7 @@
         <v>00284F</v>
       </c>
     </row>
-    <row r="670" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="670" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B670" s="2">
         <v>646</v>
       </c>
@@ -12476,7 +12476,7 @@
         <v>00285F</v>
       </c>
     </row>
-    <row r="671" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="671" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B671" s="2">
         <v>647</v>
       </c>
@@ -12489,7 +12489,7 @@
         <v>00286F</v>
       </c>
     </row>
-    <row r="672" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="672" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B672" s="2">
         <v>648</v>
       </c>
@@ -12502,7 +12502,7 @@
         <v>00287F</v>
       </c>
     </row>
-    <row r="673" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="673" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B673" s="2">
         <v>649</v>
       </c>
@@ -12515,7 +12515,7 @@
         <v>00288F</v>
       </c>
     </row>
-    <row r="674" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="674" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B674" s="2">
         <v>650</v>
       </c>
@@ -12528,7 +12528,7 @@
         <v>00289F</v>
       </c>
     </row>
-    <row r="675" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="675" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B675" s="2">
         <v>651</v>
       </c>
@@ -12541,7 +12541,7 @@
         <v>0028AF</v>
       </c>
     </row>
-    <row r="676" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="676" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B676" s="2">
         <v>652</v>
       </c>
@@ -12554,7 +12554,7 @@
         <v>0028BF</v>
       </c>
     </row>
-    <row r="677" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="677" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B677" s="2">
         <v>653</v>
       </c>
@@ -12567,7 +12567,7 @@
         <v>0028CF</v>
       </c>
     </row>
-    <row r="678" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="678" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B678" s="2">
         <v>654</v>
       </c>
@@ -12580,7 +12580,7 @@
         <v>0028DF</v>
       </c>
     </row>
-    <row r="679" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="679" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B679" s="2">
         <v>655</v>
       </c>
@@ -12593,7 +12593,7 @@
         <v>0028EF</v>
       </c>
     </row>
-    <row r="680" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="680" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B680" s="2">
         <v>656</v>
       </c>
@@ -12606,7 +12606,7 @@
         <v>0028FF</v>
       </c>
     </row>
-    <row r="681" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="681" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B681" s="2">
         <v>657</v>
       </c>
@@ -12619,7 +12619,7 @@
         <v>00290F</v>
       </c>
     </row>
-    <row r="682" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="682" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B682" s="2">
         <v>658</v>
       </c>
@@ -12632,7 +12632,7 @@
         <v>00291F</v>
       </c>
     </row>
-    <row r="683" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="683" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B683" s="2">
         <v>659</v>
       </c>
@@ -12645,7 +12645,7 @@
         <v>00292F</v>
       </c>
     </row>
-    <row r="684" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="684" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B684" s="2">
         <v>660</v>
       </c>
@@ -12658,7 +12658,7 @@
         <v>00293F</v>
       </c>
     </row>
-    <row r="685" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="685" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B685" s="2">
         <v>661</v>
       </c>
@@ -12671,7 +12671,7 @@
         <v>00294F</v>
       </c>
     </row>
-    <row r="686" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="686" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B686" s="2">
         <v>662</v>
       </c>
@@ -12684,7 +12684,7 @@
         <v>00295F</v>
       </c>
     </row>
-    <row r="687" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="687" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B687" s="2">
         <v>663</v>
       </c>
@@ -12697,7 +12697,7 @@
         <v>00296F</v>
       </c>
     </row>
-    <row r="688" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="688" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B688" s="2">
         <v>664</v>
       </c>
@@ -12710,7 +12710,7 @@
         <v>00297F</v>
       </c>
     </row>
-    <row r="689" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="689" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B689" s="2">
         <v>665</v>
       </c>
@@ -12723,7 +12723,7 @@
         <v>00298F</v>
       </c>
     </row>
-    <row r="690" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="690" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B690" s="2">
         <v>666</v>
       </c>
@@ -12736,7 +12736,7 @@
         <v>00299F</v>
       </c>
     </row>
-    <row r="691" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="691" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B691" s="2">
         <v>667</v>
       </c>
@@ -12749,7 +12749,7 @@
         <v>0029AF</v>
       </c>
     </row>
-    <row r="692" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="692" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B692" s="2">
         <v>668</v>
       </c>
@@ -12762,7 +12762,7 @@
         <v>0029BF</v>
       </c>
     </row>
-    <row r="693" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="693" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B693" s="2">
         <v>669</v>
       </c>
@@ -12775,7 +12775,7 @@
         <v>0029CF</v>
       </c>
     </row>
-    <row r="694" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="694" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B694" s="2">
         <v>670</v>
       </c>
@@ -12788,7 +12788,7 @@
         <v>0029DF</v>
       </c>
     </row>
-    <row r="695" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="695" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B695" s="2">
         <v>671</v>
       </c>
@@ -12801,7 +12801,7 @@
         <v>0029EF</v>
       </c>
     </row>
-    <row r="696" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="696" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B696" s="2">
         <v>672</v>
       </c>
@@ -12814,7 +12814,7 @@
         <v>0029FF</v>
       </c>
     </row>
-    <row r="697" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="697" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B697" s="2">
         <v>673</v>
       </c>
@@ -12827,7 +12827,7 @@
         <v>002A0F</v>
       </c>
     </row>
-    <row r="698" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="698" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B698" s="2">
         <v>674</v>
       </c>
@@ -12840,7 +12840,7 @@
         <v>002A1F</v>
       </c>
     </row>
-    <row r="699" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="699" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B699" s="2">
         <v>675</v>
       </c>
@@ -12853,7 +12853,7 @@
         <v>002A2F</v>
       </c>
     </row>
-    <row r="700" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="700" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B700" s="2">
         <v>676</v>
       </c>
@@ -12866,7 +12866,7 @@
         <v>002A3F</v>
       </c>
     </row>
-    <row r="701" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="701" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B701" s="2">
         <v>677</v>
       </c>
@@ -12879,7 +12879,7 @@
         <v>002A4F</v>
       </c>
     </row>
-    <row r="702" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="702" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B702" s="2">
         <v>678</v>
       </c>
@@ -12892,7 +12892,7 @@
         <v>002A5F</v>
       </c>
     </row>
-    <row r="703" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="703" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B703" s="2">
         <v>679</v>
       </c>
@@ -12905,7 +12905,7 @@
         <v>002A6F</v>
       </c>
     </row>
-    <row r="704" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="704" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B704" s="2">
         <v>680</v>
       </c>
@@ -12918,7 +12918,7 @@
         <v>002A7F</v>
       </c>
     </row>
-    <row r="705" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="705" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B705" s="2">
         <v>681</v>
       </c>
@@ -12931,7 +12931,7 @@
         <v>002A8F</v>
       </c>
     </row>
-    <row r="706" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="706" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B706" s="2">
         <v>682</v>
       </c>
@@ -12944,7 +12944,7 @@
         <v>002A9F</v>
       </c>
     </row>
-    <row r="707" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="707" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B707" s="2">
         <v>683</v>
       </c>
@@ -12957,7 +12957,7 @@
         <v>002AAF</v>
       </c>
     </row>
-    <row r="708" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="708" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B708" s="2">
         <v>684</v>
       </c>
@@ -12970,7 +12970,7 @@
         <v>002ABF</v>
       </c>
     </row>
-    <row r="709" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="709" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B709" s="2">
         <v>685</v>
       </c>
@@ -12983,7 +12983,7 @@
         <v>002ACF</v>
       </c>
     </row>
-    <row r="710" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="710" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B710" s="2">
         <v>686</v>
       </c>
@@ -12996,7 +12996,7 @@
         <v>002ADF</v>
       </c>
     </row>
-    <row r="711" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="711" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B711" s="2">
         <v>687</v>
       </c>
@@ -13009,7 +13009,7 @@
         <v>002AEF</v>
       </c>
     </row>
-    <row r="712" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="712" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B712" s="2">
         <v>688</v>
       </c>
@@ -13022,7 +13022,7 @@
         <v>002AFF</v>
       </c>
     </row>
-    <row r="713" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="713" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B713" s="2">
         <v>689</v>
       </c>
@@ -13035,7 +13035,7 @@
         <v>002B0F</v>
       </c>
     </row>
-    <row r="714" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="714" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B714" s="2">
         <v>690</v>
       </c>
@@ -13048,7 +13048,7 @@
         <v>002B1F</v>
       </c>
     </row>
-    <row r="715" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="715" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B715" s="2">
         <v>691</v>
       </c>
@@ -13061,7 +13061,7 @@
         <v>002B2F</v>
       </c>
     </row>
-    <row r="716" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="716" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B716" s="2">
         <v>692</v>
       </c>
@@ -13074,7 +13074,7 @@
         <v>002B3F</v>
       </c>
     </row>
-    <row r="717" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="717" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B717" s="2">
         <v>693</v>
       </c>
@@ -13087,7 +13087,7 @@
         <v>002B4F</v>
       </c>
     </row>
-    <row r="718" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="718" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B718" s="2">
         <v>694</v>
       </c>
@@ -13100,7 +13100,7 @@
         <v>002B5F</v>
       </c>
     </row>
-    <row r="719" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="719" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B719" s="2">
         <v>695</v>
       </c>
@@ -13113,7 +13113,7 @@
         <v>002B6F</v>
       </c>
     </row>
-    <row r="720" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="720" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B720" s="2">
         <v>696</v>
       </c>
@@ -13126,7 +13126,7 @@
         <v>002B7F</v>
       </c>
     </row>
-    <row r="721" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="721" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B721" s="2">
         <v>697</v>
       </c>
@@ -13139,7 +13139,7 @@
         <v>002B8F</v>
       </c>
     </row>
-    <row r="722" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="722" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B722" s="2">
         <v>698</v>
       </c>
@@ -13152,7 +13152,7 @@
         <v>002B9F</v>
       </c>
     </row>
-    <row r="723" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="723" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B723" s="2">
         <v>699</v>
       </c>
@@ -13165,7 +13165,7 @@
         <v>002BAF</v>
       </c>
     </row>
-    <row r="724" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="724" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B724" s="2">
         <v>700</v>
       </c>
@@ -13178,7 +13178,7 @@
         <v>002BBF</v>
       </c>
     </row>
-    <row r="725" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="725" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B725" s="2">
         <v>701</v>
       </c>
@@ -13191,7 +13191,7 @@
         <v>002BCF</v>
       </c>
     </row>
-    <row r="726" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="726" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B726" s="2">
         <v>702</v>
       </c>
@@ -13204,7 +13204,7 @@
         <v>002BDF</v>
       </c>
     </row>
-    <row r="727" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="727" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B727" s="2">
         <v>703</v>
       </c>
@@ -13217,7 +13217,7 @@
         <v>002BEF</v>
       </c>
     </row>
-    <row r="728" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="728" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B728" s="2">
         <v>704</v>
       </c>
@@ -13230,7 +13230,7 @@
         <v>002BFF</v>
       </c>
     </row>
-    <row r="729" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="729" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B729" s="2">
         <v>705</v>
       </c>
@@ -13243,7 +13243,7 @@
         <v>002C0F</v>
       </c>
     </row>
-    <row r="730" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="730" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B730" s="2">
         <v>706</v>
       </c>
@@ -13256,7 +13256,7 @@
         <v>002C1F</v>
       </c>
     </row>
-    <row r="731" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="731" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B731" s="2">
         <v>707</v>
       </c>
@@ -13269,7 +13269,7 @@
         <v>002C2F</v>
       </c>
     </row>
-    <row r="732" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="732" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B732" s="2">
         <v>708</v>
       </c>
@@ -13282,7 +13282,7 @@
         <v>002C3F</v>
       </c>
     </row>
-    <row r="733" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="733" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B733" s="2">
         <v>709</v>
       </c>
@@ -13295,7 +13295,7 @@
         <v>002C4F</v>
       </c>
     </row>
-    <row r="734" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="734" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B734" s="2">
         <v>710</v>
       </c>
@@ -13308,7 +13308,7 @@
         <v>002C5F</v>
       </c>
     </row>
-    <row r="735" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="735" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B735" s="2">
         <v>711</v>
       </c>
@@ -13321,7 +13321,7 @@
         <v>002C6F</v>
       </c>
     </row>
-    <row r="736" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="736" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B736" s="2">
         <v>712</v>
       </c>
@@ -13334,7 +13334,7 @@
         <v>002C7F</v>
       </c>
     </row>
-    <row r="737" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="737" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B737" s="2">
         <v>713</v>
       </c>
@@ -13347,7 +13347,7 @@
         <v>002C8F</v>
       </c>
     </row>
-    <row r="738" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="738" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B738" s="2">
         <v>714</v>
       </c>
@@ -13360,7 +13360,7 @@
         <v>002C9F</v>
       </c>
     </row>
-    <row r="739" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="739" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B739" s="2">
         <v>715</v>
       </c>
@@ -13373,7 +13373,7 @@
         <v>002CAF</v>
       </c>
     </row>
-    <row r="740" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="740" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B740" s="2">
         <v>716</v>
       </c>
@@ -13386,7 +13386,7 @@
         <v>002CBF</v>
       </c>
     </row>
-    <row r="741" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="741" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B741" s="2">
         <v>717</v>
       </c>
@@ -13399,7 +13399,7 @@
         <v>002CCF</v>
       </c>
     </row>
-    <row r="742" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="742" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B742" s="2">
         <v>718</v>
       </c>
@@ -13412,7 +13412,7 @@
         <v>002CDF</v>
       </c>
     </row>
-    <row r="743" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="743" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B743" s="2">
         <v>719</v>
       </c>
@@ -13425,7 +13425,7 @@
         <v>002CEF</v>
       </c>
     </row>
-    <row r="744" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="744" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B744" s="2">
         <v>720</v>
       </c>
@@ -13438,7 +13438,7 @@
         <v>002CFF</v>
       </c>
     </row>
-    <row r="745" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="745" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B745" s="2">
         <v>721</v>
       </c>
@@ -13451,7 +13451,7 @@
         <v>002D0F</v>
       </c>
     </row>
-    <row r="746" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="746" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B746" s="2">
         <v>722</v>
       </c>
@@ -13464,7 +13464,7 @@
         <v>002D1F</v>
       </c>
     </row>
-    <row r="747" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="747" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B747" s="2">
         <v>723</v>
       </c>
@@ -13477,7 +13477,7 @@
         <v>002D2F</v>
       </c>
     </row>
-    <row r="748" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="748" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B748" s="2">
         <v>724</v>
       </c>
@@ -13490,7 +13490,7 @@
         <v>002D3F</v>
       </c>
     </row>
-    <row r="749" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="749" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B749" s="2">
         <v>725</v>
       </c>
@@ -13503,7 +13503,7 @@
         <v>002D4F</v>
       </c>
     </row>
-    <row r="750" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="750" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B750" s="2">
         <v>726</v>
       </c>
@@ -13516,7 +13516,7 @@
         <v>002D5F</v>
       </c>
     </row>
-    <row r="751" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="751" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B751" s="2">
         <v>727</v>
       </c>
@@ -13529,7 +13529,7 @@
         <v>002D6F</v>
       </c>
     </row>
-    <row r="752" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="752" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B752" s="2">
         <v>728</v>
       </c>
@@ -13542,7 +13542,7 @@
         <v>002D7F</v>
       </c>
     </row>
-    <row r="753" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="753" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B753" s="2">
         <v>729</v>
       </c>
@@ -13555,7 +13555,7 @@
         <v>002D8F</v>
       </c>
     </row>
-    <row r="754" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="754" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B754" s="2">
         <v>730</v>
       </c>
@@ -13568,7 +13568,7 @@
         <v>002D9F</v>
       </c>
     </row>
-    <row r="755" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="755" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B755" s="2">
         <v>731</v>
       </c>
@@ -13581,7 +13581,7 @@
         <v>002DAF</v>
       </c>
     </row>
-    <row r="756" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="756" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B756" s="2">
         <v>732</v>
       </c>
@@ -13594,7 +13594,7 @@
         <v>002DBF</v>
       </c>
     </row>
-    <row r="757" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="757" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B757" s="2">
         <v>733</v>
       </c>
@@ -13607,7 +13607,7 @@
         <v>002DCF</v>
       </c>
     </row>
-    <row r="758" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="758" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B758" s="2">
         <v>734</v>
       </c>
@@ -13620,7 +13620,7 @@
         <v>002DDF</v>
       </c>
     </row>
-    <row r="759" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="759" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B759" s="2">
         <v>735</v>
       </c>
@@ -13633,7 +13633,7 @@
         <v>002DEF</v>
       </c>
     </row>
-    <row r="760" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="760" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B760" s="2">
         <v>736</v>
       </c>
@@ -13646,7 +13646,7 @@
         <v>002DFF</v>
       </c>
     </row>
-    <row r="761" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="761" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B761" s="2">
         <v>737</v>
       </c>
@@ -13659,7 +13659,7 @@
         <v>002E0F</v>
       </c>
     </row>
-    <row r="762" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="762" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B762" s="2">
         <v>738</v>
       </c>
@@ -13672,7 +13672,7 @@
         <v>002E1F</v>
       </c>
     </row>
-    <row r="763" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="763" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B763" s="2">
         <v>739</v>
       </c>
@@ -13685,7 +13685,7 @@
         <v>002E2F</v>
       </c>
     </row>
-    <row r="764" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="764" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B764" s="2">
         <v>740</v>
       </c>
@@ -13698,7 +13698,7 @@
         <v>002E3F</v>
       </c>
     </row>
-    <row r="765" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="765" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B765" s="2">
         <v>741</v>
       </c>
@@ -13711,7 +13711,7 @@
         <v>002E4F</v>
       </c>
     </row>
-    <row r="766" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="766" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B766" s="2">
         <v>742</v>
       </c>
@@ -13724,7 +13724,7 @@
         <v>002E5F</v>
       </c>
     </row>
-    <row r="767" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="767" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B767" s="2">
         <v>743</v>
       </c>
@@ -13737,7 +13737,7 @@
         <v>002E6F</v>
       </c>
     </row>
-    <row r="768" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="768" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B768" s="2">
         <v>744</v>
       </c>
@@ -13750,7 +13750,7 @@
         <v>002E7F</v>
       </c>
     </row>
-    <row r="769" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="769" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B769" s="2">
         <v>745</v>
       </c>
@@ -13763,7 +13763,7 @@
         <v>002E8F</v>
       </c>
     </row>
-    <row r="770" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="770" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B770" s="2">
         <v>746</v>
       </c>
@@ -13776,7 +13776,7 @@
         <v>002E9F</v>
       </c>
     </row>
-    <row r="771" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="771" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B771" s="2">
         <v>747</v>
       </c>
@@ -13789,7 +13789,7 @@
         <v>002EAF</v>
       </c>
     </row>
-    <row r="772" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="772" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B772" s="2">
         <v>748</v>
       </c>
@@ -13802,7 +13802,7 @@
         <v>002EBF</v>
       </c>
     </row>
-    <row r="773" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="773" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B773" s="2">
         <v>749</v>
       </c>
@@ -13815,7 +13815,7 @@
         <v>002ECF</v>
       </c>
     </row>
-    <row r="774" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="774" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B774" s="2">
         <v>750</v>
       </c>
@@ -13828,7 +13828,7 @@
         <v>002EDF</v>
       </c>
     </row>
-    <row r="775" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="775" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B775" s="2">
         <v>751</v>
       </c>
@@ -13841,7 +13841,7 @@
         <v>002EEF</v>
       </c>
     </row>
-    <row r="776" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="776" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B776" s="2">
         <v>752</v>
       </c>
@@ -13854,7 +13854,7 @@
         <v>002EFF</v>
       </c>
     </row>
-    <row r="777" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="777" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B777" s="2">
         <v>753</v>
       </c>
@@ -13867,7 +13867,7 @@
         <v>002F0F</v>
       </c>
     </row>
-    <row r="778" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="778" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B778" s="2">
         <v>754</v>
       </c>
@@ -13880,7 +13880,7 @@
         <v>002F1F</v>
       </c>
     </row>
-    <row r="779" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="779" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B779" s="2">
         <v>755</v>
       </c>
@@ -13893,7 +13893,7 @@
         <v>002F2F</v>
       </c>
     </row>
-    <row r="780" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="780" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B780" s="2">
         <v>756</v>
       </c>
@@ -13906,7 +13906,7 @@
         <v>002F3F</v>
       </c>
     </row>
-    <row r="781" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="781" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B781" s="2">
         <v>757</v>
       </c>
@@ -13919,7 +13919,7 @@
         <v>002F4F</v>
       </c>
     </row>
-    <row r="782" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="782" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B782" s="2">
         <v>758</v>
       </c>
@@ -13932,7 +13932,7 @@
         <v>002F5F</v>
       </c>
     </row>
-    <row r="783" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="783" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B783" s="2">
         <v>759</v>
       </c>
@@ -13945,7 +13945,7 @@
         <v>002F6F</v>
       </c>
     </row>
-    <row r="784" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="784" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B784" s="2">
         <v>760</v>
       </c>
@@ -13958,7 +13958,7 @@
         <v>002F7F</v>
       </c>
     </row>
-    <row r="785" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="785" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B785" s="2">
         <v>761</v>
       </c>
@@ -13971,7 +13971,7 @@
         <v>002F8F</v>
       </c>
     </row>
-    <row r="786" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="786" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B786" s="2">
         <v>762</v>
       </c>
@@ -13984,7 +13984,7 @@
         <v>002F9F</v>
       </c>
     </row>
-    <row r="787" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="787" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B787" s="2">
         <v>763</v>
       </c>
@@ -13997,7 +13997,7 @@
         <v>002FAF</v>
       </c>
     </row>
-    <row r="788" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="788" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B788" s="2">
         <v>764</v>
       </c>
@@ -14010,7 +14010,7 @@
         <v>002FBF</v>
       </c>
     </row>
-    <row r="789" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="789" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B789" s="2">
         <v>765</v>
       </c>
@@ -14023,7 +14023,7 @@
         <v>002FCF</v>
       </c>
     </row>
-    <row r="790" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="790" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B790" s="2">
         <v>766</v>
       </c>
@@ -14036,7 +14036,7 @@
         <v>002FDF</v>
       </c>
     </row>
-    <row r="791" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="791" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B791" s="2">
         <v>767</v>
       </c>
@@ -14049,7 +14049,7 @@
         <v>002FEF</v>
       </c>
     </row>
-    <row r="792" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="792" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B792" s="2">
         <v>768</v>
       </c>
@@ -14062,7 +14062,7 @@
         <v>002FFF</v>
       </c>
     </row>
-    <row r="793" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="793" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B793" s="2">
         <v>769</v>
       </c>
@@ -14075,7 +14075,7 @@
         <v>00300F</v>
       </c>
     </row>
-    <row r="794" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="794" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B794" s="2">
         <v>770</v>
       </c>
@@ -14088,7 +14088,7 @@
         <v>00301F</v>
       </c>
     </row>
-    <row r="795" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="795" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B795" s="2">
         <v>771</v>
       </c>
@@ -14101,7 +14101,7 @@
         <v>00302F</v>
       </c>
     </row>
-    <row r="796" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="796" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B796" s="2">
         <v>772</v>
       </c>
@@ -14114,7 +14114,7 @@
         <v>00303F</v>
       </c>
     </row>
-    <row r="797" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="797" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B797" s="2">
         <v>773</v>
       </c>
@@ -14127,7 +14127,7 @@
         <v>00304F</v>
       </c>
     </row>
-    <row r="798" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="798" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B798" s="2">
         <v>774</v>
       </c>
@@ -14140,7 +14140,7 @@
         <v>00305F</v>
       </c>
     </row>
-    <row r="799" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="799" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B799" s="2">
         <v>775</v>
       </c>
@@ -14153,7 +14153,7 @@
         <v>00306F</v>
       </c>
     </row>
-    <row r="800" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="800" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B800" s="2">
         <v>776</v>
       </c>
@@ -14166,7 +14166,7 @@
         <v>00307F</v>
       </c>
     </row>
-    <row r="801" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="801" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B801" s="2">
         <v>777</v>
       </c>
@@ -14179,7 +14179,7 @@
         <v>00308F</v>
       </c>
     </row>
-    <row r="802" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="802" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B802" s="2">
         <v>778</v>
       </c>
@@ -14192,7 +14192,7 @@
         <v>00309F</v>
       </c>
     </row>
-    <row r="803" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="803" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B803" s="2">
         <v>779</v>
       </c>
@@ -14205,7 +14205,7 @@
         <v>0030AF</v>
       </c>
     </row>
-    <row r="804" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="804" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B804" s="2">
         <v>780</v>
       </c>
@@ -14218,7 +14218,7 @@
         <v>0030BF</v>
       </c>
     </row>
-    <row r="805" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="805" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B805" s="2">
         <v>781</v>
       </c>
@@ -14231,7 +14231,7 @@
         <v>0030CF</v>
       </c>
     </row>
-    <row r="806" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="806" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B806" s="2">
         <v>782</v>
       </c>
@@ -14244,7 +14244,7 @@
         <v>0030DF</v>
       </c>
     </row>
-    <row r="807" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="807" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B807" s="2">
         <v>783</v>
       </c>
@@ -14257,7 +14257,7 @@
         <v>0030EF</v>
       </c>
     </row>
-    <row r="808" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="808" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B808" s="2">
         <v>784</v>
       </c>
@@ -14270,7 +14270,7 @@
         <v>0030FF</v>
       </c>
     </row>
-    <row r="809" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="809" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B809" s="2">
         <v>785</v>
       </c>
@@ -14283,7 +14283,7 @@
         <v>00310F</v>
       </c>
     </row>
-    <row r="810" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="810" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B810" s="2">
         <v>786</v>
       </c>
@@ -14296,7 +14296,7 @@
         <v>00311F</v>
       </c>
     </row>
-    <row r="811" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="811" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B811" s="2">
         <v>787</v>
       </c>
@@ -14309,7 +14309,7 @@
         <v>00312F</v>
       </c>
     </row>
-    <row r="812" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="812" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B812" s="2">
         <v>788</v>
       </c>
@@ -14322,7 +14322,7 @@
         <v>00313F</v>
       </c>
     </row>
-    <row r="813" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="813" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B813" s="2">
         <v>789</v>
       </c>
@@ -14335,7 +14335,7 @@
         <v>00314F</v>
       </c>
     </row>
-    <row r="814" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="814" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B814" s="2">
         <v>790</v>
       </c>
@@ -14348,7 +14348,7 @@
         <v>00315F</v>
       </c>
     </row>
-    <row r="815" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="815" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B815" s="2">
         <v>791</v>
       </c>
@@ -14361,7 +14361,7 @@
         <v>00316F</v>
       </c>
     </row>
-    <row r="816" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="816" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B816" s="2">
         <v>792</v>
       </c>
@@ -14374,7 +14374,7 @@
         <v>00317F</v>
       </c>
     </row>
-    <row r="817" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="817" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B817" s="2">
         <v>793</v>
       </c>
@@ -14387,7 +14387,7 @@
         <v>00318F</v>
       </c>
     </row>
-    <row r="818" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="818" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B818" s="2">
         <v>794</v>
       </c>
@@ -14400,7 +14400,7 @@
         <v>00319F</v>
       </c>
     </row>
-    <row r="819" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="819" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B819" s="2">
         <v>795</v>
       </c>
@@ -14413,7 +14413,7 @@
         <v>0031AF</v>
       </c>
     </row>
-    <row r="820" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="820" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B820" s="2">
         <v>796</v>
       </c>
@@ -14426,7 +14426,7 @@
         <v>0031BF</v>
       </c>
     </row>
-    <row r="821" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="821" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B821" s="2">
         <v>797</v>
       </c>
@@ -14439,7 +14439,7 @@
         <v>0031CF</v>
       </c>
     </row>
-    <row r="822" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="822" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B822" s="2">
         <v>798</v>
       </c>
@@ -14452,7 +14452,7 @@
         <v>0031DF</v>
       </c>
     </row>
-    <row r="823" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="823" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B823" s="2">
         <v>799</v>
       </c>
@@ -14465,7 +14465,7 @@
         <v>0031EF</v>
       </c>
     </row>
-    <row r="824" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="824" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B824" s="2">
         <v>800</v>
       </c>
@@ -14478,7 +14478,7 @@
         <v>0031FF</v>
       </c>
     </row>
-    <row r="825" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="825" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B825" s="2">
         <v>801</v>
       </c>
@@ -14491,7 +14491,7 @@
         <v>00320F</v>
       </c>
     </row>
-    <row r="826" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="826" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B826" s="2">
         <v>802</v>
       </c>
@@ -14504,7 +14504,7 @@
         <v>00321F</v>
       </c>
     </row>
-    <row r="827" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="827" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B827" s="2">
         <v>803</v>
       </c>
@@ -14517,7 +14517,7 @@
         <v>00322F</v>
       </c>
     </row>
-    <row r="828" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="828" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B828" s="2">
         <v>804</v>
       </c>
@@ -14530,7 +14530,7 @@
         <v>00323F</v>
       </c>
     </row>
-    <row r="829" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="829" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B829" s="2">
         <v>805</v>
       </c>
@@ -14543,7 +14543,7 @@
         <v>00324F</v>
       </c>
     </row>
-    <row r="830" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="830" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B830" s="2">
         <v>806</v>
       </c>
@@ -14556,7 +14556,7 @@
         <v>00325F</v>
       </c>
     </row>
-    <row r="831" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="831" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B831" s="2">
         <v>807</v>
       </c>
@@ -14569,7 +14569,7 @@
         <v>00326F</v>
       </c>
     </row>
-    <row r="832" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="832" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B832" s="2">
         <v>808</v>
       </c>
@@ -14582,7 +14582,7 @@
         <v>00327F</v>
       </c>
     </row>
-    <row r="833" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="833" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B833" s="2">
         <v>809</v>
       </c>
@@ -14595,7 +14595,7 @@
         <v>00328F</v>
       </c>
     </row>
-    <row r="834" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="834" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B834" s="2">
         <v>810</v>
       </c>
@@ -14608,7 +14608,7 @@
         <v>00329F</v>
       </c>
     </row>
-    <row r="835" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="835" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B835" s="2">
         <v>811</v>
       </c>
@@ -14621,7 +14621,7 @@
         <v>0032AF</v>
       </c>
     </row>
-    <row r="836" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="836" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B836" s="2">
         <v>812</v>
       </c>
@@ -14634,7 +14634,7 @@
         <v>0032BF</v>
       </c>
     </row>
-    <row r="837" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="837" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B837" s="2">
         <v>813</v>
       </c>
@@ -14647,7 +14647,7 @@
         <v>0032CF</v>
       </c>
     </row>
-    <row r="838" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="838" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B838" s="2">
         <v>814</v>
       </c>
@@ -14660,7 +14660,7 @@
         <v>0032DF</v>
       </c>
     </row>
-    <row r="839" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="839" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B839" s="2">
         <v>815</v>
       </c>
@@ -14673,7 +14673,7 @@
         <v>0032EF</v>
       </c>
     </row>
-    <row r="840" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="840" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B840" s="2">
         <v>816</v>
       </c>
@@ -14686,7 +14686,7 @@
         <v>0032FF</v>
       </c>
     </row>
-    <row r="841" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="841" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B841" s="2">
         <v>817</v>
       </c>
@@ -14699,7 +14699,7 @@
         <v>00330F</v>
       </c>
     </row>
-    <row r="842" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="842" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B842" s="2">
         <v>818</v>
       </c>
@@ -14712,7 +14712,7 @@
         <v>00331F</v>
       </c>
     </row>
-    <row r="843" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="843" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B843" s="2">
         <v>819</v>
       </c>
@@ -14725,7 +14725,7 @@
         <v>00332F</v>
       </c>
     </row>
-    <row r="844" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="844" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B844" s="2">
         <v>820</v>
       </c>
@@ -14738,7 +14738,7 @@
         <v>00333F</v>
       </c>
     </row>
-    <row r="845" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="845" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B845" s="2">
         <v>821</v>
       </c>
@@ -14751,7 +14751,7 @@
         <v>00334F</v>
       </c>
     </row>
-    <row r="846" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="846" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B846" s="2">
         <v>822</v>
       </c>
@@ -14764,7 +14764,7 @@
         <v>00335F</v>
       </c>
     </row>
-    <row r="847" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="847" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B847" s="2">
         <v>823</v>
       </c>
@@ -14777,7 +14777,7 @@
         <v>00336F</v>
       </c>
     </row>
-    <row r="848" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="848" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B848" s="2">
         <v>824</v>
       </c>
@@ -14790,7 +14790,7 @@
         <v>00337F</v>
       </c>
     </row>
-    <row r="849" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="849" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B849" s="2">
         <v>825</v>
       </c>
@@ -14803,7 +14803,7 @@
         <v>00338F</v>
       </c>
     </row>
-    <row r="850" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="850" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B850" s="2">
         <v>826</v>
       </c>
@@ -14816,7 +14816,7 @@
         <v>00339F</v>
       </c>
     </row>
-    <row r="851" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="851" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B851" s="2">
         <v>827</v>
       </c>
@@ -14829,7 +14829,7 @@
         <v>0033AF</v>
       </c>
     </row>
-    <row r="852" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="852" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B852" s="2">
         <v>828</v>
       </c>
@@ -14842,7 +14842,7 @@
         <v>0033BF</v>
       </c>
     </row>
-    <row r="853" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="853" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B853" s="2">
         <v>829</v>
       </c>
@@ -14855,7 +14855,7 @@
         <v>0033CF</v>
       </c>
     </row>
-    <row r="854" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="854" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B854" s="2">
         <v>830</v>
       </c>
@@ -14868,7 +14868,7 @@
         <v>0033DF</v>
       </c>
     </row>
-    <row r="855" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="855" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B855" s="2">
         <v>831</v>
       </c>
@@ -14881,7 +14881,7 @@
         <v>0033EF</v>
       </c>
     </row>
-    <row r="856" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="856" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B856" s="2">
         <v>832</v>
       </c>
@@ -14894,7 +14894,7 @@
         <v>0033FF</v>
       </c>
     </row>
-    <row r="857" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="857" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B857" s="2">
         <v>833</v>
       </c>
@@ -14907,7 +14907,7 @@
         <v>00340F</v>
       </c>
     </row>
-    <row r="858" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="858" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B858" s="2">
         <v>834</v>
       </c>
@@ -14920,7 +14920,7 @@
         <v>00341F</v>
       </c>
     </row>
-    <row r="859" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="859" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B859" s="2">
         <v>835</v>
       </c>
@@ -14933,7 +14933,7 @@
         <v>00342F</v>
       </c>
     </row>
-    <row r="860" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="860" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B860" s="2">
         <v>836</v>
       </c>
@@ -14946,7 +14946,7 @@
         <v>00343F</v>
       </c>
     </row>
-    <row r="861" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="861" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B861" s="2">
         <v>837</v>
       </c>
@@ -14959,7 +14959,7 @@
         <v>00344F</v>
       </c>
     </row>
-    <row r="862" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="862" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B862" s="2">
         <v>838</v>
       </c>
@@ -14972,7 +14972,7 @@
         <v>00345F</v>
       </c>
     </row>
-    <row r="863" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="863" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B863" s="2">
         <v>839</v>
       </c>
@@ -14985,7 +14985,7 @@
         <v>00346F</v>
       </c>
     </row>
-    <row r="864" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="864" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B864" s="2">
         <v>840</v>
       </c>
@@ -14998,7 +14998,7 @@
         <v>00347F</v>
       </c>
     </row>
-    <row r="865" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="865" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B865" s="2">
         <v>841</v>
       </c>
@@ -15011,7 +15011,7 @@
         <v>00348F</v>
       </c>
     </row>
-    <row r="866" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="866" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B866" s="2">
         <v>842</v>
       </c>
@@ -15024,7 +15024,7 @@
         <v>00349F</v>
       </c>
     </row>
-    <row r="867" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="867" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B867" s="2">
         <v>843</v>
       </c>
@@ -15037,7 +15037,7 @@
         <v>0034AF</v>
       </c>
     </row>
-    <row r="868" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="868" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B868" s="2">
         <v>844</v>
       </c>
@@ -15050,7 +15050,7 @@
         <v>0034BF</v>
       </c>
     </row>
-    <row r="869" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="869" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B869" s="2">
         <v>845</v>
       </c>
@@ -15063,7 +15063,7 @@
         <v>0034CF</v>
       </c>
     </row>
-    <row r="870" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="870" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B870" s="2">
         <v>846</v>
       </c>
@@ -15076,7 +15076,7 @@
         <v>0034DF</v>
       </c>
     </row>
-    <row r="871" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="871" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B871" s="2">
         <v>847</v>
       </c>
@@ -15089,7 +15089,7 @@
         <v>0034EF</v>
       </c>
     </row>
-    <row r="872" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="872" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B872" s="2">
         <v>848</v>
       </c>
@@ -15102,7 +15102,7 @@
         <v>0034FF</v>
       </c>
     </row>
-    <row r="873" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="873" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B873" s="2">
         <v>849</v>
       </c>
@@ -15115,7 +15115,7 @@
         <v>00350F</v>
       </c>
     </row>
-    <row r="874" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="874" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B874" s="2">
         <v>850</v>
       </c>
@@ -15128,7 +15128,7 @@
         <v>00351F</v>
       </c>
     </row>
-    <row r="875" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="875" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B875" s="2">
         <v>851</v>
       </c>
@@ -15141,7 +15141,7 @@
         <v>00352F</v>
       </c>
     </row>
-    <row r="876" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="876" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B876" s="2">
         <v>852</v>
       </c>
@@ -15154,7 +15154,7 @@
         <v>00353F</v>
       </c>
     </row>
-    <row r="877" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="877" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B877" s="2">
         <v>853</v>
       </c>
@@ -15167,7 +15167,7 @@
         <v>00354F</v>
       </c>
     </row>
-    <row r="878" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="878" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B878" s="2">
         <v>854</v>
       </c>
@@ -15180,7 +15180,7 @@
         <v>00355F</v>
       </c>
     </row>
-    <row r="879" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="879" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B879" s="2">
         <v>855</v>
       </c>
@@ -15193,7 +15193,7 @@
         <v>00356F</v>
       </c>
     </row>
-    <row r="880" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="880" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B880" s="2">
         <v>856</v>
       </c>
@@ -15206,7 +15206,7 @@
         <v>00357F</v>
       </c>
     </row>
-    <row r="881" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="881" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B881" s="2">
         <v>857</v>
       </c>
@@ -15219,7 +15219,7 @@
         <v>00358F</v>
       </c>
     </row>
-    <row r="882" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="882" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B882" s="2">
         <v>858</v>
       </c>
@@ -15232,7 +15232,7 @@
         <v>00359F</v>
       </c>
     </row>
-    <row r="883" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="883" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B883" s="2">
         <v>859</v>
       </c>
@@ -15245,7 +15245,7 @@
         <v>0035AF</v>
       </c>
     </row>
-    <row r="884" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="884" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B884" s="2">
         <v>860</v>
       </c>
@@ -15258,7 +15258,7 @@
         <v>0035BF</v>
       </c>
     </row>
-    <row r="885" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="885" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B885" s="2">
         <v>861</v>
       </c>
@@ -15271,7 +15271,7 @@
         <v>0035CF</v>
       </c>
     </row>
-    <row r="886" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="886" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B886" s="2">
         <v>862</v>
       </c>
@@ -15284,7 +15284,7 @@
         <v>0035DF</v>
       </c>
     </row>
-    <row r="887" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="887" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B887" s="2">
         <v>863</v>
       </c>
@@ -15297,7 +15297,7 @@
         <v>0035EF</v>
       </c>
     </row>
-    <row r="888" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="888" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B888" s="2">
         <v>864</v>
       </c>
@@ -15310,7 +15310,7 @@
         <v>0035FF</v>
       </c>
     </row>
-    <row r="889" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="889" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B889" s="2">
         <v>865</v>
       </c>
@@ -15323,7 +15323,7 @@
         <v>00360F</v>
       </c>
     </row>
-    <row r="890" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="890" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B890" s="2">
         <v>866</v>
       </c>
@@ -15336,7 +15336,7 @@
         <v>00361F</v>
       </c>
     </row>
-    <row r="891" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="891" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B891" s="2">
         <v>867</v>
       </c>
@@ -15349,7 +15349,7 @@
         <v>00362F</v>
       </c>
     </row>
-    <row r="892" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="892" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B892" s="2">
         <v>868</v>
       </c>
@@ -15362,7 +15362,7 @@
         <v>00363F</v>
       </c>
     </row>
-    <row r="893" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="893" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B893" s="2">
         <v>869</v>
       </c>
@@ -15375,7 +15375,7 @@
         <v>00364F</v>
       </c>
     </row>
-    <row r="894" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="894" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B894" s="2">
         <v>870</v>
       </c>
@@ -15388,7 +15388,7 @@
         <v>00365F</v>
       </c>
     </row>
-    <row r="895" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="895" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B895" s="2">
         <v>871</v>
       </c>
@@ -15401,7 +15401,7 @@
         <v>00366F</v>
       </c>
     </row>
-    <row r="896" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="896" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B896" s="2">
         <v>872</v>
       </c>
@@ -15414,7 +15414,7 @@
         <v>00367F</v>
       </c>
     </row>
-    <row r="897" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="897" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B897" s="2">
         <v>873</v>
       </c>
@@ -15427,7 +15427,7 @@
         <v>00368F</v>
       </c>
     </row>
-    <row r="898" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="898" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B898" s="2">
         <v>874</v>
       </c>
@@ -15440,7 +15440,7 @@
         <v>00369F</v>
       </c>
     </row>
-    <row r="899" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="899" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B899" s="2">
         <v>875</v>
       </c>
@@ -15453,7 +15453,7 @@
         <v>0036AF</v>
       </c>
     </row>
-    <row r="900" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="900" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B900" s="2">
         <v>876</v>
       </c>
@@ -15466,7 +15466,7 @@
         <v>0036BF</v>
       </c>
     </row>
-    <row r="901" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="901" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B901" s="2">
         <v>877</v>
       </c>
@@ -15479,7 +15479,7 @@
         <v>0036CF</v>
       </c>
     </row>
-    <row r="902" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="902" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B902" s="2">
         <v>878</v>
       </c>
@@ -15492,7 +15492,7 @@
         <v>0036DF</v>
       </c>
     </row>
-    <row r="903" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="903" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B903" s="2">
         <v>879</v>
       </c>
@@ -15505,7 +15505,7 @@
         <v>0036EF</v>
       </c>
     </row>
-    <row r="904" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="904" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B904" s="2">
         <v>880</v>
       </c>
@@ -15518,7 +15518,7 @@
         <v>0036FF</v>
       </c>
     </row>
-    <row r="905" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="905" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B905" s="2">
         <v>881</v>
       </c>
@@ -15531,7 +15531,7 @@
         <v>00370F</v>
       </c>
     </row>
-    <row r="906" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="906" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B906" s="2">
         <v>882</v>
       </c>
@@ -15544,7 +15544,7 @@
         <v>00371F</v>
       </c>
     </row>
-    <row r="907" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="907" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B907" s="2">
         <v>883</v>
       </c>
@@ -15557,7 +15557,7 @@
         <v>00372F</v>
       </c>
     </row>
-    <row r="908" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="908" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B908" s="2">
         <v>884</v>
       </c>
@@ -15570,7 +15570,7 @@
         <v>00373F</v>
       </c>
     </row>
-    <row r="909" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="909" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B909" s="2">
         <v>885</v>
       </c>
@@ -15583,7 +15583,7 @@
         <v>00374F</v>
       </c>
     </row>
-    <row r="910" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="910" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B910" s="2">
         <v>886</v>
       </c>
@@ -15596,7 +15596,7 @@
         <v>00375F</v>
       </c>
     </row>
-    <row r="911" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="911" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B911" s="2">
         <v>887</v>
       </c>
@@ -15609,7 +15609,7 @@
         <v>00376F</v>
       </c>
     </row>
-    <row r="912" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="912" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B912" s="2">
         <v>888</v>
       </c>
@@ -15622,7 +15622,7 @@
         <v>00377F</v>
       </c>
     </row>
-    <row r="913" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="913" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B913" s="2">
         <v>889</v>
       </c>
@@ -15635,7 +15635,7 @@
         <v>00378F</v>
       </c>
     </row>
-    <row r="914" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="914" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B914" s="2">
         <v>890</v>
       </c>
@@ -15648,7 +15648,7 @@
         <v>00379F</v>
       </c>
     </row>
-    <row r="915" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="915" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B915" s="2">
         <v>891</v>
       </c>
@@ -15661,7 +15661,7 @@
         <v>0037AF</v>
       </c>
     </row>
-    <row r="916" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="916" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B916" s="2">
         <v>892</v>
       </c>
@@ -15674,7 +15674,7 @@
         <v>0037BF</v>
       </c>
     </row>
-    <row r="917" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="917" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B917" s="2">
         <v>893</v>
       </c>
@@ -15687,7 +15687,7 @@
         <v>0037CF</v>
       </c>
     </row>
-    <row r="918" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="918" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B918" s="2">
         <v>894</v>
       </c>
@@ -15700,7 +15700,7 @@
         <v>0037DF</v>
       </c>
     </row>
-    <row r="919" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="919" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B919" s="2">
         <v>895</v>
       </c>
@@ -15713,7 +15713,7 @@
         <v>0037EF</v>
       </c>
     </row>
-    <row r="920" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="920" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B920" s="2">
         <v>896</v>
       </c>
@@ -15726,7 +15726,7 @@
         <v>0037FF</v>
       </c>
     </row>
-    <row r="921" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="921" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B921" s="2">
         <v>897</v>
       </c>
@@ -15739,7 +15739,7 @@
         <v>00380F</v>
       </c>
     </row>
-    <row r="922" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="922" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B922" s="2">
         <v>898</v>
       </c>
@@ -15752,7 +15752,7 @@
         <v>00381F</v>
       </c>
     </row>
-    <row r="923" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="923" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B923" s="2">
         <v>899</v>
       </c>
@@ -15765,7 +15765,7 @@
         <v>00382F</v>
       </c>
     </row>
-    <row r="924" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="924" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B924" s="2">
         <v>900</v>
       </c>
@@ -15778,7 +15778,7 @@
         <v>00383F</v>
       </c>
     </row>
-    <row r="925" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="925" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B925" s="2">
         <v>901</v>
       </c>
@@ -15791,7 +15791,7 @@
         <v>00384F</v>
       </c>
     </row>
-    <row r="926" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="926" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B926" s="2">
         <v>902</v>
       </c>
@@ -15804,7 +15804,7 @@
         <v>00385F</v>
       </c>
     </row>
-    <row r="927" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="927" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B927" s="2">
         <v>903</v>
       </c>
@@ -15817,7 +15817,7 @@
         <v>00386F</v>
       </c>
     </row>
-    <row r="928" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="928" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B928" s="2">
         <v>904</v>
       </c>
@@ -15830,7 +15830,7 @@
         <v>00387F</v>
       </c>
     </row>
-    <row r="929" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="929" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B929" s="2">
         <v>905</v>
       </c>
@@ -15843,7 +15843,7 @@
         <v>00388F</v>
       </c>
     </row>
-    <row r="930" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="930" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B930" s="2">
         <v>906</v>
       </c>
@@ -15856,7 +15856,7 @@
         <v>00389F</v>
       </c>
     </row>
-    <row r="931" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="931" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B931" s="2">
         <v>907</v>
       </c>
@@ -15869,7 +15869,7 @@
         <v>0038AF</v>
       </c>
     </row>
-    <row r="932" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="932" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B932" s="2">
         <v>908</v>
       </c>
@@ -15882,7 +15882,7 @@
         <v>0038BF</v>
       </c>
     </row>
-    <row r="933" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="933" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B933" s="2">
         <v>909</v>
       </c>
@@ -15895,7 +15895,7 @@
         <v>0038CF</v>
       </c>
     </row>
-    <row r="934" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="934" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B934" s="2">
         <v>910</v>
       </c>
@@ -15908,7 +15908,7 @@
         <v>0038DF</v>
       </c>
     </row>
-    <row r="935" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="935" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B935" s="2">
         <v>911</v>
       </c>
@@ -15921,7 +15921,7 @@
         <v>0038EF</v>
       </c>
     </row>
-    <row r="936" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="936" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B936" s="2">
         <v>912</v>
       </c>
@@ -15934,7 +15934,7 @@
         <v>0038FF</v>
       </c>
     </row>
-    <row r="937" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="937" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B937" s="2">
         <v>913</v>
       </c>
@@ -15947,7 +15947,7 @@
         <v>00390F</v>
       </c>
     </row>
-    <row r="938" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="938" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B938" s="2">
         <v>914</v>
       </c>
@@ -15960,7 +15960,7 @@
         <v>00391F</v>
       </c>
     </row>
-    <row r="939" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="939" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B939" s="2">
         <v>915</v>
       </c>
@@ -15973,7 +15973,7 @@
         <v>00392F</v>
       </c>
     </row>
-    <row r="940" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="940" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B940" s="2">
         <v>916</v>
       </c>
@@ -15986,7 +15986,7 @@
         <v>00393F</v>
       </c>
     </row>
-    <row r="941" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="941" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B941" s="2">
         <v>917</v>
       </c>
@@ -15999,7 +15999,7 @@
         <v>00394F</v>
       </c>
     </row>
-    <row r="942" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="942" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B942" s="2">
         <v>918</v>
       </c>
@@ -16012,7 +16012,7 @@
         <v>00395F</v>
       </c>
     </row>
-    <row r="943" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="943" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B943" s="2">
         <v>919</v>
       </c>
@@ -16025,7 +16025,7 @@
         <v>00396F</v>
       </c>
     </row>
-    <row r="944" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="944" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B944" s="2">
         <v>920</v>
       </c>
@@ -16038,7 +16038,7 @@
         <v>00397F</v>
       </c>
     </row>
-    <row r="945" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="945" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B945" s="2">
         <v>921</v>
       </c>
@@ -16051,7 +16051,7 @@
         <v>00398F</v>
       </c>
     </row>
-    <row r="946" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="946" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B946" s="2">
         <v>922</v>
       </c>
@@ -16064,7 +16064,7 @@
         <v>00399F</v>
       </c>
     </row>
-    <row r="947" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="947" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B947" s="2">
         <v>923</v>
       </c>
@@ -16077,7 +16077,7 @@
         <v>0039AF</v>
       </c>
     </row>
-    <row r="948" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="948" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B948" s="2">
         <v>924</v>
       </c>
@@ -16090,7 +16090,7 @@
         <v>0039BF</v>
       </c>
     </row>
-    <row r="949" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="949" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B949" s="2">
         <v>925</v>
       </c>
@@ -16103,7 +16103,7 @@
         <v>0039CF</v>
       </c>
     </row>
-    <row r="950" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="950" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B950" s="2">
         <v>926</v>
       </c>
@@ -16116,7 +16116,7 @@
         <v>0039DF</v>
       </c>
     </row>
-    <row r="951" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="951" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B951" s="2">
         <v>927</v>
       </c>
@@ -16129,7 +16129,7 @@
         <v>0039EF</v>
       </c>
     </row>
-    <row r="952" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="952" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B952" s="2">
         <v>928</v>
       </c>
@@ -16142,7 +16142,7 @@
         <v>0039FF</v>
       </c>
     </row>
-    <row r="953" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="953" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B953" s="2">
         <v>929</v>
       </c>
@@ -16155,7 +16155,7 @@
         <v>003A0F</v>
       </c>
     </row>
-    <row r="954" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="954" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B954" s="2">
         <v>930</v>
       </c>
@@ -16168,7 +16168,7 @@
         <v>003A1F</v>
       </c>
     </row>
-    <row r="955" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="955" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B955" s="2">
         <v>931</v>
       </c>
@@ -16181,7 +16181,7 @@
         <v>003A2F</v>
       </c>
     </row>
-    <row r="956" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="956" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B956" s="2">
         <v>932</v>
       </c>
@@ -16194,7 +16194,7 @@
         <v>003A3F</v>
       </c>
     </row>
-    <row r="957" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="957" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B957" s="2">
         <v>933</v>
       </c>
@@ -16207,7 +16207,7 @@
         <v>003A4F</v>
       </c>
     </row>
-    <row r="958" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="958" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B958" s="2">
         <v>934</v>
       </c>
@@ -16220,7 +16220,7 @@
         <v>003A5F</v>
       </c>
     </row>
-    <row r="959" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="959" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B959" s="2">
         <v>935</v>
       </c>
@@ -16233,7 +16233,7 @@
         <v>003A6F</v>
       </c>
     </row>
-    <row r="960" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="960" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B960" s="2">
         <v>936</v>
       </c>
@@ -16246,7 +16246,7 @@
         <v>003A7F</v>
       </c>
     </row>
-    <row r="961" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="961" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B961" s="2">
         <v>937</v>
       </c>
@@ -16259,7 +16259,7 @@
         <v>003A8F</v>
       </c>
     </row>
-    <row r="962" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="962" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B962" s="2">
         <v>938</v>
       </c>
@@ -16272,7 +16272,7 @@
         <v>003A9F</v>
       </c>
     </row>
-    <row r="963" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="963" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B963" s="2">
         <v>939</v>
       </c>
@@ -16285,7 +16285,7 @@
         <v>003AAF</v>
       </c>
     </row>
-    <row r="964" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="964" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B964" s="2">
         <v>940</v>
       </c>
@@ -16298,7 +16298,7 @@
         <v>003ABF</v>
       </c>
     </row>
-    <row r="965" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="965" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B965" s="2">
         <v>941</v>
       </c>
@@ -16311,7 +16311,7 @@
         <v>003ACF</v>
       </c>
     </row>
-    <row r="966" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="966" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B966" s="2">
         <v>942</v>
       </c>
@@ -16324,7 +16324,7 @@
         <v>003ADF</v>
       </c>
     </row>
-    <row r="967" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="967" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B967" s="2">
         <v>943</v>
       </c>
@@ -16337,7 +16337,7 @@
         <v>003AEF</v>
       </c>
     </row>
-    <row r="968" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="968" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B968" s="2">
         <v>944</v>
       </c>
@@ -16350,7 +16350,7 @@
         <v>003AFF</v>
       </c>
     </row>
-    <row r="969" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="969" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B969" s="2">
         <v>945</v>
       </c>
@@ -16363,7 +16363,7 @@
         <v>003B0F</v>
       </c>
     </row>
-    <row r="970" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="970" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B970" s="2">
         <v>946</v>
       </c>
@@ -16376,7 +16376,7 @@
         <v>003B1F</v>
       </c>
     </row>
-    <row r="971" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="971" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B971" s="2">
         <v>947</v>
       </c>
@@ -16389,7 +16389,7 @@
         <v>003B2F</v>
       </c>
     </row>
-    <row r="972" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="972" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B972" s="2">
         <v>948</v>
       </c>
@@ -16402,7 +16402,7 @@
         <v>003B3F</v>
       </c>
     </row>
-    <row r="973" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="973" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B973" s="2">
         <v>949</v>
       </c>
@@ -16415,7 +16415,7 @@
         <v>003B4F</v>
       </c>
     </row>
-    <row r="974" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="974" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B974" s="2">
         <v>950</v>
       </c>
@@ -16428,7 +16428,7 @@
         <v>003B5F</v>
       </c>
     </row>
-    <row r="975" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="975" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B975" s="2">
         <v>951</v>
       </c>
@@ -16441,7 +16441,7 @@
         <v>003B6F</v>
       </c>
     </row>
-    <row r="976" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="976" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B976" s="2">
         <v>952</v>
       </c>
@@ -16454,7 +16454,7 @@
         <v>003B7F</v>
       </c>
     </row>
-    <row r="977" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="977" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B977" s="2">
         <v>953</v>
       </c>
@@ -16467,7 +16467,7 @@
         <v>003B8F</v>
       </c>
     </row>
-    <row r="978" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="978" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B978" s="2">
         <v>954</v>
       </c>
@@ -16480,7 +16480,7 @@
         <v>003B9F</v>
       </c>
     </row>
-    <row r="979" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="979" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B979" s="2">
         <v>955</v>
       </c>
@@ -16493,7 +16493,7 @@
         <v>003BAF</v>
       </c>
     </row>
-    <row r="980" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="980" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B980" s="2">
         <v>956</v>
       </c>
@@ -16506,7 +16506,7 @@
         <v>003BBF</v>
       </c>
     </row>
-    <row r="981" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="981" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B981" s="2">
         <v>957</v>
       </c>
@@ -16519,7 +16519,7 @@
         <v>003BCF</v>
       </c>
     </row>
-    <row r="982" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="982" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B982" s="2">
         <v>958</v>
       </c>
@@ -16532,7 +16532,7 @@
         <v>003BDF</v>
       </c>
     </row>
-    <row r="983" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="983" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B983" s="2">
         <v>959</v>
       </c>
@@ -16545,7 +16545,7 @@
         <v>003BEF</v>
       </c>
     </row>
-    <row r="984" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="984" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B984" s="2">
         <v>960</v>
       </c>
@@ -16558,7 +16558,7 @@
         <v>003BFF</v>
       </c>
     </row>
-    <row r="985" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="985" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B985" s="2">
         <v>961</v>
       </c>
@@ -16571,7 +16571,7 @@
         <v>003C0F</v>
       </c>
     </row>
-    <row r="986" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="986" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B986" s="2">
         <v>962</v>
       </c>
@@ -16584,7 +16584,7 @@
         <v>003C1F</v>
       </c>
     </row>
-    <row r="987" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="987" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B987" s="2">
         <v>963</v>
       </c>
@@ -16597,7 +16597,7 @@
         <v>003C2F</v>
       </c>
     </row>
-    <row r="988" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="988" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B988" s="2">
         <v>964</v>
       </c>
@@ -16610,7 +16610,7 @@
         <v>003C3F</v>
       </c>
     </row>
-    <row r="989" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="989" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B989" s="2">
         <v>965</v>
       </c>
@@ -16623,7 +16623,7 @@
         <v>003C4F</v>
       </c>
     </row>
-    <row r="990" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="990" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B990" s="2">
         <v>966</v>
       </c>
@@ -16636,7 +16636,7 @@
         <v>003C5F</v>
       </c>
     </row>
-    <row r="991" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="991" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B991" s="2">
         <v>967</v>
       </c>
@@ -16649,7 +16649,7 @@
         <v>003C6F</v>
       </c>
     </row>
-    <row r="992" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="992" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B992" s="2">
         <v>968</v>
       </c>
@@ -16662,7 +16662,7 @@
         <v>003C7F</v>
       </c>
     </row>
-    <row r="993" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="993" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B993" s="2">
         <v>969</v>
       </c>
@@ -16675,7 +16675,7 @@
         <v>003C8F</v>
       </c>
     </row>
-    <row r="994" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="994" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B994" s="2">
         <v>970</v>
       </c>
@@ -16688,7 +16688,7 @@
         <v>003C9F</v>
       </c>
     </row>
-    <row r="995" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="995" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B995" s="2">
         <v>971</v>
       </c>
@@ -16701,7 +16701,7 @@
         <v>003CAF</v>
       </c>
     </row>
-    <row r="996" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="996" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B996" s="2">
         <v>972</v>
       </c>
@@ -16714,7 +16714,7 @@
         <v>003CBF</v>
       </c>
     </row>
-    <row r="997" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="997" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B997" s="2">
         <v>973</v>
       </c>
@@ -16727,7 +16727,7 @@
         <v>003CCF</v>
       </c>
     </row>
-    <row r="998" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="998" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B998" s="2">
         <v>974</v>
       </c>
@@ -16740,7 +16740,7 @@
         <v>003CDF</v>
       </c>
     </row>
-    <row r="999" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="999" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B999" s="2">
         <v>975</v>
       </c>
@@ -16753,7 +16753,7 @@
         <v>003CEF</v>
       </c>
     </row>
-    <row r="1000" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="1000" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B1000" s="2">
         <v>976</v>
       </c>
@@ -16766,7 +16766,7 @@
         <v>003CFF</v>
       </c>
     </row>
-    <row r="1001" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="1001" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B1001" s="2">
         <v>977</v>
       </c>
@@ -16779,7 +16779,7 @@
         <v>003D0F</v>
       </c>
     </row>
-    <row r="1002" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="1002" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B1002" s="2">
         <v>978</v>
       </c>
@@ -16792,7 +16792,7 @@
         <v>003D1F</v>
       </c>
     </row>
-    <row r="1003" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="1003" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B1003" s="2">
         <v>979</v>
       </c>
@@ -16805,7 +16805,7 @@
         <v>003D2F</v>
       </c>
     </row>
-    <row r="1004" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="1004" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B1004" s="2">
         <v>980</v>
       </c>
@@ -16818,7 +16818,7 @@
         <v>003D3F</v>
       </c>
     </row>
-    <row r="1005" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="1005" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B1005" s="2">
         <v>981</v>
       </c>
@@ -16831,7 +16831,7 @@
         <v>003D4F</v>
       </c>
     </row>
-    <row r="1006" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="1006" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B1006" s="2">
         <v>982</v>
       </c>
@@ -16844,7 +16844,7 @@
         <v>003D5F</v>
       </c>
     </row>
-    <row r="1007" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="1007" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B1007" s="2">
         <v>983</v>
       </c>
@@ -16857,7 +16857,7 @@
         <v>003D6F</v>
       </c>
     </row>
-    <row r="1008" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="1008" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B1008" s="2">
         <v>984</v>
       </c>
@@ -16870,7 +16870,7 @@
         <v>003D7F</v>
       </c>
     </row>
-    <row r="1009" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="1009" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B1009" s="2">
         <v>985</v>
       </c>
@@ -16883,7 +16883,7 @@
         <v>003D8F</v>
       </c>
     </row>
-    <row r="1010" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="1010" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B1010" s="2">
         <v>986</v>
       </c>
@@ -16896,7 +16896,7 @@
         <v>003D9F</v>
       </c>
     </row>
-    <row r="1011" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="1011" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B1011" s="2">
         <v>987</v>
       </c>
@@ -16909,7 +16909,7 @@
         <v>003DAF</v>
       </c>
     </row>
-    <row r="1012" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="1012" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B1012" s="2">
         <v>988</v>
       </c>
@@ -16922,7 +16922,7 @@
         <v>003DBF</v>
       </c>
     </row>
-    <row r="1013" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="1013" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B1013" s="2">
         <v>989</v>
       </c>
@@ -16935,7 +16935,7 @@
         <v>003DCF</v>
       </c>
     </row>
-    <row r="1014" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="1014" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B1014" s="2">
         <v>990</v>
       </c>
@@ -16948,7 +16948,7 @@
         <v>003DDF</v>
       </c>
     </row>
-    <row r="1015" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="1015" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B1015" s="2">
         <v>991</v>
       </c>
@@ -16961,7 +16961,7 @@
         <v>003DEF</v>
       </c>
     </row>
-    <row r="1016" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="1016" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B1016" s="2">
         <v>992</v>
       </c>
@@ -16974,7 +16974,7 @@
         <v>003DFF</v>
       </c>
     </row>
-    <row r="1017" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="1017" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B1017" s="2">
         <v>993</v>
       </c>
@@ -16987,7 +16987,7 @@
         <v>003E0F</v>
       </c>
     </row>
-    <row r="1018" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="1018" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B1018" s="2">
         <v>994</v>
       </c>
@@ -17000,7 +17000,7 @@
         <v>003E1F</v>
       </c>
     </row>
-    <row r="1019" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="1019" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B1019" s="2">
         <v>995</v>
       </c>
@@ -17013,7 +17013,7 @@
         <v>003E2F</v>
       </c>
     </row>
-    <row r="1020" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="1020" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B1020" s="2">
         <v>996</v>
       </c>
@@ -17026,7 +17026,7 @@
         <v>003E3F</v>
       </c>
     </row>
-    <row r="1021" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="1021" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B1021" s="2">
         <v>997</v>
       </c>
@@ -17039,7 +17039,7 @@
         <v>003E4F</v>
       </c>
     </row>
-    <row r="1022" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="1022" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B1022" s="2">
         <v>998</v>
       </c>
@@ -17052,7 +17052,7 @@
         <v>003E5F</v>
       </c>
     </row>
-    <row r="1023" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="1023" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B1023" s="2">
         <v>999</v>
       </c>
@@ -17065,7 +17065,7 @@
         <v>003E6F</v>
       </c>
     </row>
-    <row r="1024" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="1024" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B1024" s="2">
         <v>1000</v>
       </c>
@@ -17078,7 +17078,7 @@
         <v>003E7F</v>
       </c>
     </row>
-    <row r="1025" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="1025" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B1025" s="2">
         <v>1001</v>
       </c>
@@ -17091,7 +17091,7 @@
         <v>003E8F</v>
       </c>
     </row>
-    <row r="1026" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="1026" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B1026" s="2">
         <v>1002</v>
       </c>
@@ -17104,7 +17104,7 @@
         <v>003E9F</v>
       </c>
     </row>
-    <row r="1027" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="1027" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B1027" s="2">
         <v>1003</v>
       </c>
@@ -17117,7 +17117,7 @@
         <v>003EAF</v>
       </c>
     </row>
-    <row r="1028" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="1028" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B1028" s="2">
         <v>1004</v>
       </c>
@@ -17130,7 +17130,7 @@
         <v>003EBF</v>
       </c>
     </row>
-    <row r="1029" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="1029" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B1029" s="2">
         <v>1005</v>
       </c>
@@ -17143,7 +17143,7 @@
         <v>003ECF</v>
       </c>
     </row>
-    <row r="1030" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="1030" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B1030" s="2">
         <v>1006</v>
       </c>
@@ -17156,7 +17156,7 @@
         <v>003EDF</v>
       </c>
     </row>
-    <row r="1031" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="1031" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B1031" s="2">
         <v>1007</v>
       </c>
@@ -17169,7 +17169,7 @@
         <v>003EEF</v>
       </c>
     </row>
-    <row r="1032" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="1032" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B1032" s="2">
         <v>1008</v>
       </c>
@@ -17182,7 +17182,7 @@
         <v>003EFF</v>
       </c>
     </row>
-    <row r="1033" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="1033" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B1033" s="2">
         <v>1009</v>
       </c>
@@ -17195,7 +17195,7 @@
         <v>003F0F</v>
       </c>
     </row>
-    <row r="1034" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="1034" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B1034" s="2">
         <v>1010</v>
       </c>
@@ -17208,7 +17208,7 @@
         <v>003F1F</v>
       </c>
     </row>
-    <row r="1035" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="1035" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B1035" s="2">
         <v>1011</v>
       </c>
@@ -17221,7 +17221,7 @@
         <v>003F2F</v>
       </c>
     </row>
-    <row r="1036" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="1036" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B1036" s="2">
         <v>1012</v>
       </c>
@@ -17234,7 +17234,7 @@
         <v>003F3F</v>
       </c>
     </row>
-    <row r="1037" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="1037" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B1037" s="2">
         <v>1013</v>
       </c>
@@ -17247,7 +17247,7 @@
         <v>003F4F</v>
       </c>
     </row>
-    <row r="1038" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="1038" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B1038" s="2">
         <v>1014</v>
       </c>
@@ -17260,7 +17260,7 @@
         <v>003F5F</v>
       </c>
     </row>
-    <row r="1039" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="1039" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B1039" s="2">
         <v>1015</v>
       </c>
@@ -17273,7 +17273,7 @@
         <v>003F6F</v>
       </c>
     </row>
-    <row r="1040" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="1040" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B1040" s="2">
         <v>1016</v>
       </c>
@@ -17286,7 +17286,7 @@
         <v>003F7F</v>
       </c>
     </row>
-    <row r="1041" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="1041" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B1041" s="2">
         <v>1017</v>
       </c>
@@ -17299,7 +17299,7 @@
         <v>003F8F</v>
       </c>
     </row>
-    <row r="1042" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="1042" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B1042" s="2">
         <v>1018</v>
       </c>
@@ -17312,7 +17312,7 @@
         <v>003F9F</v>
       </c>
     </row>
-    <row r="1043" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="1043" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B1043" s="2">
         <v>1019</v>
       </c>
@@ -17325,7 +17325,7 @@
         <v>003FAF</v>
       </c>
     </row>
-    <row r="1044" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="1044" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B1044" s="2">
         <v>1020</v>
       </c>
@@ -17338,7 +17338,7 @@
         <v>003FBF</v>
       </c>
     </row>
-    <row r="1045" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="1045" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B1045" s="2">
         <v>1021</v>
       </c>
@@ -17351,7 +17351,7 @@
         <v>003FCF</v>
       </c>
     </row>
-    <row r="1046" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="1046" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B1046" s="2">
         <v>1022</v>
       </c>
@@ -17364,7 +17364,7 @@
         <v>003FDF</v>
       </c>
     </row>
-    <row r="1047" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="1047" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B1047" s="2">
         <v>1023</v>
       </c>
@@ -17377,7 +17377,7 @@
         <v>003FEF</v>
       </c>
     </row>
-    <row r="1048" spans="2:8" x14ac:dyDescent="0.25">
+    <row r="1048" spans="2:8" x14ac:dyDescent="0.3">
       <c r="B1048" s="2">
         <v>1024</v>
       </c>
